--- a/Procesos_Grafico.xlsx
+++ b/Procesos_Grafico.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l_moya\Downloads\python_analisis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748A9287-FF4A-4179-B7AB-50BAF04C8F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58922A2-99C6-4A35-89E3-D6DE30662EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Procesos" sheetId="2" r:id="rId1"/>
+    <sheet name="Granel" sheetId="2" r:id="rId1"/>
     <sheet name="Matriz de Complejidad" sheetId="8" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
   <si>
     <t>Procesos</t>
   </si>
@@ -118,15 +118,6 @@
     <t>Tiempo en meses</t>
   </si>
   <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Media</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baja </t>
-  </si>
-  <si>
     <t>Cambio de razón social</t>
   </si>
   <si>
@@ -229,9 +220,6 @@
     <t>4+</t>
   </si>
   <si>
-    <t>3-4</t>
-  </si>
-  <si>
     <t>BAJA: 1-2</t>
   </si>
   <si>
@@ -241,7 +229,7 @@
     <t>ALTA: 4+</t>
   </si>
   <si>
-    <t>1-2</t>
+    <t>Fecha Inicio</t>
   </si>
 </sst>
 </file>
@@ -253,7 +241,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="[&lt;4]&quot;Baja: &quot;0.0;[&lt;7]&quot;Media: &quot;0.0;&quot;Alta: &quot;0.0"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -318,13 +306,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -337,14 +318,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <u/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -362,7 +335,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -387,14 +360,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -502,37 +469,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
@@ -585,9 +528,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -603,9 +543,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -615,7 +552,7 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -625,14 +562,11 @@
     <xf numFmtId="10" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -640,173 +574,99 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment readingOrder="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="50">
     <dxf>
       <font>
-        <color rgb="FF4D2200"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF542E00"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF4D2200"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF542E00"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
@@ -823,9 +683,9 @@
         <vertAlign val="baseline"/>
         <sz val="10"/>
         <color theme="1"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <fill>
@@ -835,7 +695,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
         </left>
@@ -847,6 +707,169 @@
         </top>
         <bottom/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF4D2200"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF542E00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF4D2200"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF542E00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
     <dxf>
       <font>
@@ -1120,15 +1143,6 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1137,51 +1151,44 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
+          <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
+          <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
+          <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
+          <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
+          <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
+          <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
     </dxf>
@@ -1198,7 +1205,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
+          <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
     </dxf>
@@ -1212,59 +1219,13 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
+          <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <numFmt numFmtId="166" formatCode="[&lt;4]&quot;Baja: &quot;0.0;[&lt;7]&quot;Media: &quot;0.0;&quot;Alta: &quot;0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
-        </ext>
-      </extLst>
     </dxf>
     <dxf>
       <font>
@@ -1481,7 +1442,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Procesos!$A$2:$A$6</c:f>
+              <c:f>Granel!$A$2:$A$6</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1504,7 +1465,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Procesos!$P$2:$P$6</c:f>
+              <c:f>Granel!$P$2:$P$6</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1518,7 +1479,7 @@
                   <c:v>0.3906</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.3906</c:v>
+                  <c:v>0.53120000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.1875</c:v>
@@ -2262,16 +2223,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1089024</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>136523</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>92528</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>501649</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1490435</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:rowOff>115207</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2319,54 +2280,46 @@
   </bag>
   <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
     <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
       <bagId>5</bagId>
-      <bagId>2</bagId>
     </a>
   </bag>
 </FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}" name="Tabla8" displayName="Tabla8" ref="A1:V6" totalsRowShown="0" headerRowDxfId="51">
-  <autoFilter ref="A1:V6" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}"/>
-  <tableColumns count="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}" name="Tabla8" displayName="Tabla8" ref="A1:T6" totalsRowShown="0" headerRowDxfId="49">
+  <autoFilter ref="A1:T6" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}"/>
+  <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{9D6B40D3-3215-4E98-A9FC-D478FB63C1BA}" name="Procesos"/>
     <tableColumn id="6" xr3:uid="{F5B3BD05-8E49-49F1-93DE-92D27F1C49E6}" name="Líder"/>
-    <tableColumn id="15" xr3:uid="{1EA989C9-73CA-4A22-B626-AC262B041ED9}" name="¿Contenido dentro de una iniciativa?" dataDxfId="50"/>
-    <tableColumn id="19" xr3:uid="{C9D6E896-9CBC-4057-9F81-12423CB4D99E}" name="Fecha Iniciativa" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{EEDD7810-0171-43A9-9288-43A6DF88CC68}" name="Status del proceso" dataDxfId="48"/>
-    <tableColumn id="3" xr3:uid="{234448FA-6E6F-424A-931A-3653E7178265}" name="Complejidad" dataDxfId="47">
+    <tableColumn id="15" xr3:uid="{1EA989C9-73CA-4A22-B626-AC262B041ED9}" name="¿Contenido dentro de una iniciativa?" dataDxfId="5"/>
+    <tableColumn id="19" xr3:uid="{C9D6E896-9CBC-4057-9F81-12423CB4D99E}" name="Fecha Iniciativa" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{EEDD7810-0171-43A9-9288-43A6DF88CC68}" name="Status del proceso" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{234448FA-6E6F-424A-931A-3653E7178265}" name="Complejidad" dataDxfId="48">
       <calculatedColumnFormula>Tabla4[[#This Row],[Puntaje Final (1-10)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5A4FFE81-7563-4F38-8BE5-EA30FC7C196D}" name="To-be" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{35D54FDE-D4BF-4FD2-9479-B2182C98B6D5}" name="As-is" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{E6EB2333-E84F-41CE-8EAC-52D77BF66F44}" name="Notas" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{8112EDF6-BC89-4919-A355-D2D3D1BF34BA}" name="Levantar información" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{2EA9FA24-C3F1-4C14-A867-A6FAC65E747C}" name="Armar diagrama" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{CD6D287B-BCEC-45D9-8EB8-A0F76A9F8CAF}" name="Validar diagrama" dataDxfId="41"/>
-    <tableColumn id="7" xr3:uid="{F4FF766B-5291-4082-A0FF-A66586E7C142}" name="Mejorar proceso" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{0C5A0591-A510-455E-AD87-7F86245A682D}" name="Validar mejora" dataDxfId="39"/>
-    <tableColumn id="12" xr3:uid="{C63E8C68-557E-49A9-8D27-236FDCB340BC}" name="Implementación" dataDxfId="38"/>
-    <tableColumn id="16" xr3:uid="{8B4C9571-AFDF-4088-806A-0420B7E2442E}" name="% de avance" dataDxfId="37" dataCellStyle="Porcentaje">
+    <tableColumn id="4" xr3:uid="{5A4FFE81-7563-4F38-8BE5-EA30FC7C196D}" name="To-be" dataDxfId="47"/>
+    <tableColumn id="11" xr3:uid="{35D54FDE-D4BF-4FD2-9479-B2182C98B6D5}" name="As-is" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{E6EB2333-E84F-41CE-8EAC-52D77BF66F44}" name="Notas" dataDxfId="45"/>
+    <tableColumn id="14" xr3:uid="{8112EDF6-BC89-4919-A355-D2D3D1BF34BA}" name="Levantar información" dataDxfId="44"/>
+    <tableColumn id="13" xr3:uid="{2EA9FA24-C3F1-4C14-A867-A6FAC65E747C}" name="Armar diagrama" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{CD6D287B-BCEC-45D9-8EB8-A0F76A9F8CAF}" name="Validar diagrama" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{F4FF766B-5291-4082-A0FF-A66586E7C142}" name="Mejorar proceso" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{0C5A0591-A510-455E-AD87-7F86245A682D}" name="Validar mejora" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{C63E8C68-557E-49A9-8D27-236FDCB340BC}" name="Implementación" dataDxfId="39"/>
+    <tableColumn id="16" xr3:uid="{8B4C9571-AFDF-4088-806A-0420B7E2442E}" name="% de avance" dataDxfId="2" dataCellStyle="Porcentaje">
       <calculatedColumnFormula array="1">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{B6DD48A4-1AB9-4C6E-A7E2-D52D8502F05C}" name="Tiempo bruto de levantamiento " dataDxfId="36">
+    <tableColumn id="20" xr3:uid="{7CE675F8-BCC9-4D91-AE6F-A7A6A1C260DD}" name="Fecha Inicio" dataDxfId="0" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{B6DD48A4-1AB9-4C6E-A7E2-D52D8502F05C}" name="Tiempo bruto de levantamiento " dataDxfId="1">
       <calculatedColumnFormula>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{97833884-FD4C-49EA-8567-FE1DD15B1ED4}" name="Tiempo especifico en semanas" dataDxfId="35">
+    <tableColumn id="17" xr3:uid="{97833884-FD4C-49EA-8567-FE1DD15B1ED4}" name="Tiempo especifico en semanas" dataDxfId="38">
       <calculatedColumnFormula>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{79F26D04-CE30-49F5-B63D-964F30F64CC4}" name="Tiempo en meses" dataDxfId="34">
+    <tableColumn id="18" xr3:uid="{79F26D04-CE30-49F5-B63D-964F30F64CC4}" name="Tiempo en meses" dataDxfId="37">
       <calculatedColumnFormula>(6.5 + (F2 - 1) * 0.9444) / 4.345</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="20" xr3:uid="{238ADAC1-4D7D-4EE9-9F04-653E2CEC6E2C}" name="Alta" dataDxfId="33">
-      <calculatedColumnFormula array="1">IF('Matriz de Complejidad'!H2="Alta", 'Matriz de Complejidad'!G2, _xludf.NA())</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="21" xr3:uid="{1B9E0E99-6A84-4351-8E80-31D3EFF596C1}" name="Media" dataDxfId="32">
-      <calculatedColumnFormula array="1">IF('Matriz de Complejidad'!H2="Media", 'Matriz de Complejidad'!G2, _xludf.NA())</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="22" xr3:uid="{A449FBD2-A5AB-41EE-B36C-A3EFC33B4B05}" name="Baja " dataDxfId="31">
-      <calculatedColumnFormula array="1">IF('Matriz de Complejidad'!H2="Baja", 'Matriz de Complejidad'!G2, _xludf.NA())</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2374,33 +2327,33 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}" name="Tabla3" displayName="Tabla3" ref="J10:N17" totalsRowShown="0" headerRowDxfId="30" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27" totalsRowBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}" name="Tabla3" displayName="Tabla3" ref="J10:N17" totalsRowShown="0" headerRowDxfId="36" dataDxfId="34" headerRowBorderDxfId="35" tableBorderDxfId="33" totalsRowBorderDxfId="32">
   <autoFilter ref="J10:N17" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{22A678DC-4FD4-457E-BF2F-A5B26AF5A9EF}" name="Columna" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{20414C72-C442-4898-9B74-EA7858B03946}" name="Celda" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{BA1EDFE7-FD4C-4A18-B24F-51500610B0F3}" name="Promedio" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{18E92589-EFEA-448D-8CFF-7A861810DB8E}" name="Peso (%)" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{D9FEA8B4-A59E-4AC5-9FA6-A99F7AA97E09}" name="Factor Decimal" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{22A678DC-4FD4-457E-BF2F-A5B26AF5A9EF}" name="Columna" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{20414C72-C442-4898-9B74-EA7858B03946}" name="Celda" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{BA1EDFE7-FD4C-4A18-B24F-51500610B0F3}" name="Promedio" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{18E92589-EFEA-448D-8CFF-7A861810DB8E}" name="Peso (%)" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{D9FEA8B4-A59E-4AC5-9FA6-A99F7AA97E09}" name="Factor Decimal" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4FD466F-89DF-47BA-AC9E-559F47CB9595}" name="Tabla4" displayName="Tabla4" ref="A1:H6" totalsRowShown="0" headerRowDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4FD466F-89DF-47BA-AC9E-559F47CB9595}" name="Tabla4" displayName="Tabla4" ref="A1:H6" totalsRowShown="0" headerRowDxfId="26">
   <autoFilter ref="A1:H6" xr:uid="{A4FD466F-89DF-47BA-AC9E-559F47CB9595}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{209BC8CE-A4E5-4EAD-9176-25919D421EE7}" name="Proceso" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{AD141033-AAC8-430E-AED3-EE13742AEDEF}" name="Áreas Involucradas (25%)" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{81BAF825-E86C-4EAB-83B0-4BEF6E690DAF}" name="Contenido dentro de una iniciativa (20%)" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{BD9A8428-D2BF-47C3-8A4D-000DDA7085B1}" name="¿Requiere desarrollo tecnologico? (20%)" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{CC386173-731D-4092-A2CC-5DFC807607AC}" name="¿Es un levantamiento nuevo? (15%)" dataDxfId="15"/>
-    <tableColumn id="7" xr3:uid="{44DB2B51-5EBC-435E-B533-35DBC727260D}" name="¿Toca un proceso clave? (20%)" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{91CAEE15-D755-4AEE-BD7E-76CF718F3FEF}" name="Puntaje Final (1-10)" dataDxfId="13">
+    <tableColumn id="1" xr3:uid="{209BC8CE-A4E5-4EAD-9176-25919D421EE7}" name="Proceso" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{AD141033-AAC8-430E-AED3-EE13742AEDEF}" name="Áreas Involucradas (25%)" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{81BAF825-E86C-4EAB-83B0-4BEF6E690DAF}" name="Contenido dentro de una iniciativa (20%)" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{BD9A8428-D2BF-47C3-8A4D-000DDA7085B1}" name="¿Requiere desarrollo tecnologico? (20%)" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{CC386173-731D-4092-A2CC-5DFC807607AC}" name="¿Es un levantamiento nuevo? (15%)" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{44DB2B51-5EBC-435E-B533-35DBC727260D}" name="¿Toca un proceso clave? (20%)" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{91CAEE15-D755-4AEE-BD7E-76CF718F3FEF}" name="Puntaje Final (1-10)" dataDxfId="20">
       <calculatedColumnFormula>IF(B2="", "", 10 * ( (MATCH(B2, {"1-2";"3-4";"4+"}, 0)/3)*0.25 + N(C2)*0.2 + N(D2)*0.2 + N(E2)*0.15 + N(F2)*0.2 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{83E13230-22E5-49E0-9B92-C34352FB3731}" name="Complejidad" dataDxfId="12">
+    <tableColumn id="4" xr3:uid="{83E13230-22E5-49E0-9B92-C34352FB3731}" name="Complejidad" dataDxfId="19">
       <calculatedColumnFormula>+IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&lt;=4,"Baja",IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&gt;7,"Alta","Media"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2693,13 +2646,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AED4591-DDAA-4945-939F-A4AF72524E54}">
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:T46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="27.453125" customWidth="1"/>
+    <col min="1" max="1" width="30.54296875" customWidth="1"/>
     <col min="2" max="2" width="38.7265625" customWidth="1"/>
     <col min="3" max="3" width="45.81640625" customWidth="1"/>
-    <col min="4" max="4" width="32.453125" customWidth="1"/>
+    <col min="4" max="4" width="32.453125" style="40" customWidth="1"/>
     <col min="5" max="5" width="23.26953125" customWidth="1"/>
     <col min="6" max="6" width="22.7265625" customWidth="1"/>
     <col min="7" max="7" width="24.81640625" customWidth="1"/>
@@ -2708,14 +2661,13 @@
     <col min="10" max="11" width="22.7265625" customWidth="1"/>
     <col min="12" max="14" width="24.1796875" customWidth="1"/>
     <col min="15" max="16" width="22.7265625" customWidth="1"/>
-    <col min="17" max="17" width="32" customWidth="1"/>
-    <col min="18" max="18" width="30.453125" customWidth="1"/>
-    <col min="19" max="19" width="29.453125" customWidth="1"/>
-    <col min="20" max="20" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.81640625" style="40" customWidth="1"/>
+    <col min="18" max="18" width="32" customWidth="1"/>
+    <col min="19" max="19" width="30.453125" customWidth="1"/>
+    <col min="20" max="20" width="29.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2725,7 +2677,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="37" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -2764,37 +2716,31 @@
       <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="C2" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="38"/>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="17">
+      <c r="F2" s="16">
         <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
         <v>8.5</v>
       </c>
@@ -2823,47 +2769,38 @@
       <c r="O2" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="P2" s="27" cm="1">
+      <c r="P2" s="25" cm="1">
         <f t="array" ref="P2">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</f>
         <v>0.76560000000000006</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="41">
+        <v>45992</v>
+      </c>
+      <c r="R2" s="3">
         <f>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</f>
         <v>15</v>
       </c>
-      <c r="R2" s="6">
+      <c r="S2" s="6">
         <f>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</f>
         <v>13.583333333333332</v>
       </c>
-      <c r="S2" s="6">
+      <c r="T2" s="6">
         <f>(6.5 + (F2 - 1) * 0.9444) / 4.345</f>
         <v>3.1261219792865367</v>
       </c>
-      <c r="T2" cm="1">
-        <f t="array" ref="T2">IF('Matriz de Complejidad'!H2="Alta", 'Matriz de Complejidad'!G2, _xludf.NA())</f>
-        <v>8.5</v>
-      </c>
-      <c r="U2" t="e" cm="1">
-        <f t="array" aca="1" ref="U2" ca="1">IF('Matriz de Complejidad'!H2="Media", 'Matriz de Complejidad'!G2, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="V2" t="e" cm="1">
-        <f t="array" aca="1" ref="V2" ca="1">IF('Matriz de Complejidad'!H2="Baja", 'Matriz de Complejidad'!G2, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="C3" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="38"/>
       <c r="E3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="17">
+        <v>20</v>
+      </c>
+      <c r="F3" s="16">
         <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
         <v>6.5</v>
       </c>
@@ -2892,49 +2829,40 @@
       <c r="O3" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="P3" s="27" cm="1">
+      <c r="P3" s="25" cm="1">
         <f t="array" ref="P3">+SUMPRODUCT(--(J3:O3),TRANSPOSE($N$11:$N$16))</f>
         <v>0.3906</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="41">
+        <v>45999</v>
+      </c>
+      <c r="R3" s="3">
         <f>IF(F3&lt;=3, 6.5, IF(F3&lt;=7, 10.5, 15))</f>
         <v>10.5</v>
       </c>
-      <c r="R3" s="6">
+      <c r="S3" s="6">
         <f>6.5 + (F3 - 1) * ((15 - 6.5) / (10 - 1))</f>
         <v>11.694444444444445</v>
       </c>
-      <c r="S3" s="6">
+      <c r="T3" s="6">
         <f>(6.5 + (F3 - 1) * 0.9444) / 4.345</f>
         <v>2.6914154200230151</v>
       </c>
-      <c r="T3" t="e" cm="1">
-        <f t="array" aca="1" ref="T3" ca="1">IF('Matriz de Complejidad'!H3="Alta", 'Matriz de Complejidad'!G3, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="U3" cm="1">
-        <f t="array" ref="U3">IF('Matriz de Complejidad'!H3="Media", 'Matriz de Complejidad'!G3, _xludf.NA())</f>
-        <v>6.5</v>
-      </c>
-      <c r="V3" t="e" cm="1">
-        <f t="array" aca="1" ref="V3" ca="1">IF('Matriz de Complejidad'!H3="Baja", 'Matriz de Complejidad'!G3, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4"/>
+    </row>
+    <row r="4" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="38"/>
       <c r="E4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="17">
+        <v>20</v>
+      </c>
+      <c r="F4" s="16">
         <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
-        <v>5.1666666666666661</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="G4" s="7" t="b">
         <v>0</v>
@@ -2961,49 +2889,40 @@
       <c r="O4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="P4" s="27" cm="1">
+      <c r="P4" s="25" cm="1">
         <f t="array" ref="P4">+SUMPRODUCT(--(J4:O4),TRANSPOSE($N$11:$N$16))</f>
         <v>0.3906</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="41">
+        <v>46006</v>
+      </c>
+      <c r="R4" s="3">
         <f>IF(F4&lt;=3, 6.5, IF(F4&lt;=7, 10.5, 15))</f>
         <v>10.5</v>
       </c>
-      <c r="R4" s="6">
+      <c r="S4" s="6">
         <f>6.5 + (F4 - 1) * ((15 - 6.5) / (10 - 1))</f>
-        <v>10.435185185185185</v>
-      </c>
-      <c r="S4" s="6">
+        <v>11.222222222222223</v>
+      </c>
+      <c r="T4" s="6">
         <f>(6.5 + (F4 - 1) * 0.9444) / 4.345</f>
-        <v>2.4016110471806673</v>
-      </c>
-      <c r="T4" t="e" cm="1">
-        <f t="array" aca="1" ref="T4" ca="1">IF('Matriz de Complejidad'!H4="Alta", 'Matriz de Complejidad'!G4, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="U4" cm="1">
-        <f t="array" ref="U4">IF('Matriz de Complejidad'!H4="Media", 'Matriz de Complejidad'!G4, _xludf.NA())</f>
-        <v>5.1666666666666661</v>
-      </c>
-      <c r="V4" t="e" cm="1">
-        <f t="array" aca="1" ref="V4" ca="1">IF('Matriz de Complejidad'!H4="Baja", 'Matriz de Complejidad'!G4, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+        <v>2.5827387802071349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="C5" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="38"/>
       <c r="E5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="17">
+        <v>20</v>
+      </c>
+      <c r="F5" s="16">
         <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
-        <v>1.6666666666666665</v>
+        <v>2.5</v>
       </c>
       <c r="G5" s="7" t="b">
         <v>0</v>
@@ -3025,54 +2944,46 @@
         <v>0</v>
       </c>
       <c r="N5" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O5" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="P5" s="27" cm="1">
+      <c r="P5" s="25" cm="1">
         <f t="array" ref="P5">+SUMPRODUCT(--(J5:O5),TRANSPOSE($N$11:$N$16))</f>
-        <v>0.3906</v>
-      </c>
-      <c r="Q5" s="3">
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>46027</v>
+      </c>
+      <c r="R5" s="3">
         <f>IF(F5&lt;=3, 6.5, IF(F5&lt;=7, 10.5, 15))</f>
         <v>6.5</v>
       </c>
-      <c r="R5" s="6">
+      <c r="S5" s="6">
         <f>6.5 + (F5 - 1) * ((15 - 6.5) / (10 - 1))</f>
-        <v>7.1296296296296298</v>
-      </c>
-      <c r="S5" s="6">
+        <v>7.9166666666666661</v>
+      </c>
+      <c r="T5" s="6">
         <f>(6.5 + (F5 - 1) * 0.9444) / 4.345</f>
-        <v>1.6408745684695052</v>
-      </c>
-      <c r="T5" t="e" cm="1">
-        <f t="array" aca="1" ref="T5" ca="1">IF('Matriz de Complejidad'!H5="Alta", 'Matriz de Complejidad'!G5, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="U5" t="e" cm="1">
-        <f t="array" aca="1" ref="U5" ca="1">IF('Matriz de Complejidad'!H5="Media", 'Matriz de Complejidad'!G5, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="V5" cm="1">
-        <f t="array" ref="V5">IF('Matriz de Complejidad'!H5="Baja", 'Matriz de Complejidad'!G5, _xludf.NA())</f>
-        <v>1.6666666666666665</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+        <v>1.8220023014959725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4"/>
+        <v>24</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="38"/>
       <c r="E6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="17">
+        <v>20</v>
+      </c>
+      <c r="F6" s="16">
         <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
-        <v>2.833333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="G6" s="7" t="b">
         <v>0</v>
@@ -3099,204 +3010,195 @@
       <c r="O6" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="P6" s="27" cm="1">
+      <c r="P6" s="25" cm="1">
         <f t="array" ref="P6">+SUMPRODUCT(--(J6:O6),TRANSPOSE($N$11:$N$16))</f>
         <v>0.1875</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="41">
+        <v>46048</v>
+      </c>
+      <c r="R6" s="3">
         <f>IF(F6&lt;=3, 6.5, IF(F6&lt;=7, 10.5, 15))</f>
-        <v>6.5</v>
-      </c>
-      <c r="R6" s="6">
+        <v>10.5</v>
+      </c>
+      <c r="S6" s="6">
         <f>6.5 + (F6 - 1) * ((15 - 6.5) / (10 - 1))</f>
-        <v>8.231481481481481</v>
-      </c>
-      <c r="S6" s="6">
+        <v>9.8055555555555554</v>
+      </c>
+      <c r="T6" s="6">
         <f>(6.5 + (F6 - 1) * 0.9444) / 4.345</f>
-        <v>1.8944533947065596</v>
-      </c>
-      <c r="T6" t="e" cm="1">
-        <f t="array" aca="1" ref="T6" ca="1">IF('Matriz de Complejidad'!H6="Alta", 'Matriz de Complejidad'!G6, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="U6" t="e" cm="1">
-        <f t="array" aca="1" ref="U6" ca="1">IF('Matriz de Complejidad'!H6="Media", 'Matriz de Complejidad'!G6, _xludf.NA())</f>
-        <v>#NAME?</v>
-      </c>
-      <c r="V6" cm="1">
-        <f t="array" ref="V6">IF('Matriz de Complejidad'!H6="Baja", 'Matriz de Complejidad'!G6, _xludf.NA())</f>
-        <v>2.833333333333333</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+        <v>2.2567088607594941</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
+      <c r="D7" s="39"/>
       <c r="E7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
-    <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
+      <c r="D8" s="39"/>
       <c r="E8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
+      <c r="D9" s="39"/>
       <c r="E9" s="13"/>
       <c r="F9" s="13"/>
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="18" t="s">
-        <v>28</v>
+      <c r="D10" s="39"/>
+      <c r="E10" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
       <c r="I10" s="13"/>
-      <c r="J10" s="28" t="s">
+      <c r="J10" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="N10" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="L10" s="29" t="s">
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="E11" s="17" t="s">
         <v>31</v>
-      </c>
-      <c r="M10" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="N10" s="30" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="E11" s="18" t="s">
-        <v>34</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L11" s="31">
+        <v>33</v>
+      </c>
+      <c r="L11" s="29">
         <v>2</v>
       </c>
-      <c r="M11" s="32">
+      <c r="M11" s="30">
         <v>0.1875</v>
       </c>
       <c r="N11" s="11">
         <v>0.1875</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="E12" s="19" t="s">
-        <v>37</v>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="E12" s="18" t="s">
+        <v>34</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L12" s="31">
+        <v>36</v>
+      </c>
+      <c r="L12" s="29">
         <v>0.67</v>
       </c>
-      <c r="M12" s="32">
+      <c r="M12" s="30">
         <v>6.25E-2</v>
       </c>
       <c r="N12" s="11">
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
-      <c r="F13" s="37"/>
+      <c r="F13" s="34"/>
       <c r="J13" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L13" s="31">
+        <v>38</v>
+      </c>
+      <c r="L13" s="29">
         <v>1.5</v>
       </c>
-      <c r="M13" s="32">
+      <c r="M13" s="30">
         <v>0.1406</v>
       </c>
       <c r="N13" s="11">
         <v>0.1406</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B14" s="4"/>
-      <c r="F14" s="36"/>
+      <c r="F14" s="33"/>
       <c r="J14" s="12" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" s="31">
+        <v>40</v>
+      </c>
+      <c r="L14" s="29">
         <v>4</v>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="30">
         <v>0.375</v>
       </c>
       <c r="N14" s="11">
         <v>0.375</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B15" s="4"/>
       <c r="J15" s="12" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="L15" s="31">
+        <v>42</v>
+      </c>
+      <c r="L15" s="29">
         <v>1.5</v>
       </c>
-      <c r="M15" s="32">
+      <c r="M15" s="30">
         <v>0.1406</v>
       </c>
       <c r="N15" s="11">
         <v>0.1406</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B16" s="4"/>
       <c r="J16" s="12" t="s">
         <v>14</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L16" s="31">
+        <v>43</v>
+      </c>
+      <c r="L16" s="29">
         <v>1</v>
       </c>
-      <c r="M16" s="32">
+      <c r="M16" s="30">
         <v>9.3799999999999994E-2</v>
       </c>
       <c r="N16" s="11">
         <v>9.3799999999999994E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B17" s="4"/>
-      <c r="J17" s="33" t="s">
-        <v>47</v>
-      </c>
-      <c r="K17" s="34"/>
+      <c r="J17" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="K17" s="32"/>
       <c r="L17" s="9">
         <v>10.67</v>
       </c>
@@ -3307,70 +3209,71 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B18" s="4"/>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="26"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="26"/>
-      <c r="R19" s="26"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="26"/>
-      <c r="U19" s="26"/>
-    </row>
-    <row r="20" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
-      <c r="N20" s="26"/>
-    </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="N20" s="24"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B21" s="4"/>
-      <c r="N21" s="26"/>
-    </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="N21" s="24"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B22" s="4"/>
-      <c r="N22" s="26"/>
-    </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="N22" s="24"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B23" s="4"/>
-      <c r="N23" s="26"/>
-    </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="N23" s="24"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B24" s="4"/>
-      <c r="N24" s="26"/>
-    </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="N24" s="24"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B25" s="4"/>
-      <c r="N25" s="26"/>
-    </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.35">
+      <c r="N25" s="24"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B26" s="4"/>
     </row>
-    <row r="27" spans="2:21" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
       <c r="B27" s="4"/>
+    </row>
+    <row r="46" spans="10:10" x14ac:dyDescent="0.35">
+      <c r="J46" s="33"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:D6">
-    <cfRule type="expression" dxfId="11" priority="23">
+    <cfRule type="expression" dxfId="18" priority="23">
       <formula>$H2=TRUE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="24">
+    <cfRule type="expression" dxfId="17" priority="24">
       <formula>$G2=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="9" priority="25">
+    <cfRule type="expression" dxfId="16" priority="25">
       <formula>$G2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E6 E13:E1048576">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="8" operator="equal">
       <formula>"Listo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
       <formula>"No iniciado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
       <formula>"En curso"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3386,7 +3289,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q6">
+  <conditionalFormatting sqref="R2:R6">
     <cfRule type="colorScale" priority="92">
       <colorScale>
         <cfvo type="min"/>
@@ -3398,7 +3301,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:R6">
+  <conditionalFormatting sqref="R2:S6">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -3410,7 +3313,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
+  <conditionalFormatting sqref="S2:S6">
     <cfRule type="colorScale" priority="93">
       <colorScale>
         <cfvo type="min"/>
@@ -3422,7 +3325,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S6 Q2:Q6">
+  <conditionalFormatting sqref="T2:T6 R2:R6">
     <cfRule type="colorScale" priority="94">
       <colorScale>
         <cfvo type="min"/>
@@ -3434,7 +3337,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S6">
+  <conditionalFormatting sqref="T2:T6">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -3493,42 +3396,43 @@
     <col min="5" max="5" width="39.26953125" customWidth="1"/>
     <col min="6" max="6" width="33.7265625" customWidth="1"/>
     <col min="7" max="7" width="28.7265625" customWidth="1"/>
+    <col min="8" max="8" width="21.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="E1" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="F1" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="G1" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="F1" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="H1" s="14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="38" t="b">
+        <v>19</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="35" t="b">
         <v>1</v>
       </c>
       <c r="D2" s="15" t="b">
@@ -3540,7 +3444,7 @@
       <c r="F2" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G2" s="24">
+      <c r="G2" s="22">
         <f>IF(B2="", "", 10 * ( (MATCH(B2, {"1-2";"3-4";"4+"}, 0)/3)*0.25 + N(C2)*0.2 + N(D2)*0.2 + N(E2)*0.15 + N(F2)*0.2 ))</f>
         <v>8.5</v>
       </c>
@@ -3549,12 +3453,12 @@
         <v>Alta</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>55</v>
+        <v>21</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>52</v>
       </c>
       <c r="C3" s="15" t="b">
         <v>0</v>
@@ -3568,7 +3472,7 @@
       <c r="F3" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="22">
         <f>IF(B3="", "", 10 * ( (MATCH(B3, {"1-2";"3-4";"4+"}, 0)/3)*0.25 + N(C3)*0.2 + N(D3)*0.2 + N(E3)*0.15 + N(F3)*0.2 ))</f>
         <v>6.5</v>
       </c>
@@ -3577,12 +3481,12 @@
         <v>Media</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>56</v>
+    <row r="4" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>52</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>0</v>
@@ -3596,21 +3500,21 @@
       <c r="F4" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G4" s="24">
+      <c r="G4" s="22">
         <f>IF(B4="", "", 10 * ( (MATCH(B4, {"1-2";"3-4";"4+"}, 0)/3)*0.25 + N(C4)*0.2 + N(D4)*0.2 + N(E4)*0.15 + N(F4)*0.2 ))</f>
-        <v>5.1666666666666661</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="H4" t="str">
         <f>+IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&lt;=4,"Baja",IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&gt;7,"Alta","Media"))</f>
         <v>Media</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>56</v>
+        <v>23</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>52</v>
       </c>
       <c r="C5" s="1" t="b">
         <v>0</v>
@@ -3624,21 +3528,21 @@
       <c r="F5" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="22">
         <f>IF(B5="", "", 10 * ( (MATCH(B5, {"1-2";"3-4";"4+"}, 0)/3)*0.25 + N(C5)*0.2 + N(D5)*0.2 + N(E5)*0.15 + N(F5)*0.2 ))</f>
-        <v>1.6666666666666665</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="str">
         <f>+IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&lt;=4,"Baja",IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&gt;7,"Alta","Media"))</f>
         <v>Baja</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>60</v>
+        <v>24</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>52</v>
       </c>
       <c r="C6" s="1" t="b">
         <v>0</v>
@@ -3652,60 +3556,60 @@
       <c r="F6" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="22">
         <f>IF(B6="", "", 10 * ( (MATCH(B6, {"1-2";"3-4";"4+"}, 0)/3)*0.25 + N(C6)*0.2 + N(D6)*0.2 + N(E6)*0.15 + N(F6)*0.2 ))</f>
-        <v>2.833333333333333</v>
+        <v>4.5</v>
       </c>
       <c r="H6" t="str">
         <f>+IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&lt;=4,"Baja",IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&gt;7,"Alta","Media"))</f>
-        <v>Baja</v>
+        <v>Media</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B10" s="22"/>
+      <c r="B10" s="20"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B11" s="22"/>
+      <c r="B11" s="20"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B12" s="22"/>
+      <c r="B12" s="20"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B13" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C13" s="36"/>
+      <c r="B13" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="33"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B14" s="23" t="s">
-        <v>58</v>
+      <c r="B14" s="21" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B15" s="23" t="s">
-        <v>59</v>
+      <c r="B15" s="21" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A6">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>$H2=TRUE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="11" priority="2">
       <formula>$G2=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="10" priority="3">
       <formula>$G2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"Listo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"No iniciado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"En curso"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3719,8 +3623,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Procesos_Grafico.xlsx
+++ b/Procesos_Grafico.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l_moya\Downloads\python_analisis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58922A2-99C6-4A35-89E3-D6DE30662EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95113BC-3F3F-40E8-9C8A-4737CD0F6397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Granel" sheetId="2" r:id="rId1"/>
-    <sheet name="Matriz de Complejidad" sheetId="8" r:id="rId2"/>
+    <sheet name="Envasado" sheetId="9" r:id="rId1"/>
+    <sheet name="Medidor" sheetId="10" r:id="rId2"/>
+    <sheet name="Granel" sheetId="2" r:id="rId3"/>
+    <sheet name="Matriz de Complejidad" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -59,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="57">
   <si>
     <t>Procesos</t>
   </si>
@@ -335,7 +337,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -358,6 +360,18 @@
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -475,7 +489,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <extLst>
@@ -574,7 +588,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -590,13 +604,256 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="50">
+  <dxfs count="120">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -617,8 +874,84 @@
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[&lt;4]&quot;Baja: &quot;0.0;[&lt;7]&quot;Media: &quot;0.0;&quot;Alta: &quot;0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center"/>
@@ -644,9 +977,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i/>
@@ -664,6 +994,724 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF4D2200"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF542E00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[&lt;4]&quot;Baja: &quot;0.0;[&lt;7]&quot;Media: &quot;0.0;&quot;Alta: &quot;0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF4D2200"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF542E00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF4D2200"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF542E00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF4D2200"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF542E00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="0"/>
@@ -710,169 +1758,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF4D2200"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF542E00"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF4D2200"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF542E00"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="1"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -1151,6 +2036,32 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="0"/>
@@ -1226,6 +2137,53 @@
     <dxf>
       <numFmt numFmtId="166" formatCode="[&lt;4]&quot;Baja: &quot;0.0;[&lt;7]&quot;Media: &quot;0.0;&quot;Alta: &quot;0.0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
     <dxf>
       <font>
@@ -1278,6 +2236,800 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CL"/>
+              <a:t>Avance de Procesos</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23859432685336898"/>
+          <c:y val="0.19840304182509505"/>
+          <c:w val="0.73207628450381967"/>
+          <c:h val="0.70578605430975117"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CL"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Granel!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Cambio de razón social</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Devolución por trasvasije</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bloqueo por sobregiro</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Retiro de tanque</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Gas de prueba</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Granel!$P$2:$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.76560000000000006</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3906</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3906</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.53120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1875</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6778-4302-9C43-5769F4D0A7B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1799364528"/>
+        <c:axId val="1799351088"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1799364528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1799351088"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1799351088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1799364528"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1">
+          <a:alpha val="98000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CL"/>
+              <a:t>Avance de Procesos</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.23859432685336898"/>
+          <c:y val="0.19840304182509505"/>
+          <c:w val="0.73207628450381967"/>
+          <c:h val="0.70578605430975117"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CL"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Granel!$A$2:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Cambio de razón social</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Devolución por trasvasije</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bloqueo por sobregiro</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Retiro de tanque</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Gas de prueba</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Granel!$P$2:$P$6</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.76560000000000006</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.3906</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3906</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.53120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.1875</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-03C9-4BD3-8E40-B5E284FEB8DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1799364528"/>
+        <c:axId val="1799351088"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1799364528"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1799351088"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1799351088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1799364528"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent1">
+          <a:alpha val="98000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -1714,6 +3466,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
@@ -2219,7 +4051,1103 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>136523</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>92528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1490435</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>115207</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DED61757-24C6-493D-95DD-D7ED1025AF1F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>136523</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>92528</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>1490435</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>115207</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5250C4DB-7E47-491B-A602-501E088E5C4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2288,37 +5216,37 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}" name="Tabla8" displayName="Tabla8" ref="A1:T6" totalsRowShown="0" headerRowDxfId="49">
-  <autoFilter ref="A1:T6" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{10537967-845A-432A-A796-359783753A79}" name="Tabla86" displayName="Tabla86" ref="A1:T6" totalsRowShown="0" headerRowDxfId="28">
+  <autoFilter ref="A1:T6" xr:uid="{10537967-845A-432A-A796-359783753A79}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{9D6B40D3-3215-4E98-A9FC-D478FB63C1BA}" name="Procesos"/>
-    <tableColumn id="6" xr3:uid="{F5B3BD05-8E49-49F1-93DE-92D27F1C49E6}" name="Líder"/>
-    <tableColumn id="15" xr3:uid="{1EA989C9-73CA-4A22-B626-AC262B041ED9}" name="¿Contenido dentro de una iniciativa?" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{C9D6E896-9CBC-4057-9F81-12423CB4D99E}" name="Fecha Iniciativa" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{EEDD7810-0171-43A9-9288-43A6DF88CC68}" name="Status del proceso" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{234448FA-6E6F-424A-931A-3653E7178265}" name="Complejidad" dataDxfId="48">
+    <tableColumn id="1" xr3:uid="{6C5F92E5-C3C6-4D8E-A49F-6B0B4F47A477}" name="Procesos"/>
+    <tableColumn id="6" xr3:uid="{A4A97957-CD05-4190-A7BC-FB5D702CCCF1}" name="Líder"/>
+    <tableColumn id="15" xr3:uid="{F530E09C-70F6-4AD4-9CE2-8799819B5F65}" name="¿Contenido dentro de una iniciativa?" dataDxfId="27"/>
+    <tableColumn id="19" xr3:uid="{3C563BB5-78D7-45A1-A12D-860D66970785}" name="Fecha Iniciativa" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{E521361E-8D00-4B07-BDC9-B96DE0FAAA03}" name="Status del proceso" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{D2819821-2057-4A7E-A310-4AC02854555C}" name="Complejidad" dataDxfId="24">
       <calculatedColumnFormula>Tabla4[[#This Row],[Puntaje Final (1-10)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5A4FFE81-7563-4F38-8BE5-EA30FC7C196D}" name="To-be" dataDxfId="47"/>
-    <tableColumn id="11" xr3:uid="{35D54FDE-D4BF-4FD2-9479-B2182C98B6D5}" name="As-is" dataDxfId="46"/>
-    <tableColumn id="5" xr3:uid="{E6EB2333-E84F-41CE-8EAC-52D77BF66F44}" name="Notas" dataDxfId="45"/>
-    <tableColumn id="14" xr3:uid="{8112EDF6-BC89-4919-A355-D2D3D1BF34BA}" name="Levantar información" dataDxfId="44"/>
-    <tableColumn id="13" xr3:uid="{2EA9FA24-C3F1-4C14-A867-A6FAC65E747C}" name="Armar diagrama" dataDxfId="43"/>
-    <tableColumn id="8" xr3:uid="{CD6D287B-BCEC-45D9-8EB8-A0F76A9F8CAF}" name="Validar diagrama" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{F4FF766B-5291-4082-A0FF-A66586E7C142}" name="Mejorar proceso" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{0C5A0591-A510-455E-AD87-7F86245A682D}" name="Validar mejora" dataDxfId="40"/>
-    <tableColumn id="12" xr3:uid="{C63E8C68-557E-49A9-8D27-236FDCB340BC}" name="Implementación" dataDxfId="39"/>
-    <tableColumn id="16" xr3:uid="{8B4C9571-AFDF-4088-806A-0420B7E2442E}" name="% de avance" dataDxfId="2" dataCellStyle="Porcentaje">
+    <tableColumn id="4" xr3:uid="{910659FA-862C-418A-9007-D146C6B6B684}" name="To-be" dataDxfId="23"/>
+    <tableColumn id="11" xr3:uid="{9B51737A-8E09-4796-9384-789E3D581D12}" name="As-is" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{877AE1B5-D153-435F-B52E-B1481A61A124}" name="Notas" dataDxfId="21"/>
+    <tableColumn id="14" xr3:uid="{8DE3641F-379A-4221-9320-C93224F5AC4E}" name="Levantar información" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{DE691091-0924-4E9C-9FD6-3B0C1763FCB2}" name="Armar diagrama" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{5811FC46-4802-4991-847E-0BC4C8DE7412}" name="Validar diagrama" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{751291B1-2BE5-4977-BE55-88671D59C139}" name="Mejorar proceso" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{9D1BCA4F-9FA0-4C06-9B56-EFD6A64765CF}" name="Validar mejora" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{1F59F63E-CD23-4FCF-A4B9-69F9C655A4CF}" name="Implementación" dataDxfId="15"/>
+    <tableColumn id="16" xr3:uid="{74EBFE1F-7E13-4D16-9A55-DD551B786EE1}" name="% de avance" dataDxfId="14" dataCellStyle="Porcentaje">
       <calculatedColumnFormula array="1">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{7CE675F8-BCC9-4D91-AE6F-A7A6A1C260DD}" name="Fecha Inicio" dataDxfId="0" dataCellStyle="Porcentaje"/>
-    <tableColumn id="10" xr3:uid="{B6DD48A4-1AB9-4C6E-A7E2-D52D8502F05C}" name="Tiempo bruto de levantamiento " dataDxfId="1">
+    <tableColumn id="20" xr3:uid="{337DB8B6-848F-4AFB-A923-18731D12D7EF}" name="Fecha Inicio" dataDxfId="13" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{D5F2AA22-FAE5-4AD9-A4A0-024DAA6378A6}" name="Tiempo bruto de levantamiento " dataDxfId="12">
       <calculatedColumnFormula>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{97833884-FD4C-49EA-8567-FE1DD15B1ED4}" name="Tiempo especifico en semanas" dataDxfId="38">
+    <tableColumn id="17" xr3:uid="{D61ADE36-BC70-4E92-B0A0-7B7DC901078C}" name="Tiempo especifico en semanas" dataDxfId="11">
       <calculatedColumnFormula>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{79F26D04-CE30-49F5-B63D-964F30F64CC4}" name="Tiempo en meses" dataDxfId="37">
+    <tableColumn id="18" xr3:uid="{23B9AFFA-2BB1-46FC-AE4C-6682319A6D47}" name="Tiempo en meses" dataDxfId="10">
       <calculatedColumnFormula>(6.5 + (F2 - 1) * 0.9444) / 4.345</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2327,33 +5255,139 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}" name="Tabla3" displayName="Tabla3" ref="J10:N17" totalsRowShown="0" headerRowDxfId="36" dataDxfId="34" headerRowBorderDxfId="35" tableBorderDxfId="33" totalsRowBorderDxfId="32">
-  <autoFilter ref="J10:N17" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DE26E95-1ED7-42E2-B8D7-69FDD10E3622}" name="Tabla37" displayName="Tabla37" ref="J10:N17" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="J10:N17" xr:uid="{1DE26E95-1ED7-42E2-B8D7-69FDD10E3622}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{22A678DC-4FD4-457E-BF2F-A5B26AF5A9EF}" name="Columna" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{20414C72-C442-4898-9B74-EA7858B03946}" name="Celda" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{BA1EDFE7-FD4C-4A18-B24F-51500610B0F3}" name="Promedio" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{18E92589-EFEA-448D-8CFF-7A861810DB8E}" name="Peso (%)" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{D9FEA8B4-A59E-4AC5-9FA6-A99F7AA97E09}" name="Factor Decimal" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{8CCFC06F-71F8-4178-88F3-5ABD60AE1EAE}" name="Columna" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{3F2EF7F8-BD08-4750-A577-7FD4B7C6664A}" name="Celda" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{971835D3-30F9-42D3-BEA1-520733792576}" name="Promedio" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{E2517CD1-8726-4109-92FB-1238481C74D3}" name="Peso (%)" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{A0A4FC88-C1B8-42FD-903E-A07CA6E46E3B}" name="Factor Decimal" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4FD466F-89DF-47BA-AC9E-559F47CB9595}" name="Tabla4" displayName="Tabla4" ref="A1:H6" totalsRowShown="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{11AF62AA-310D-48FE-BA1B-7667C3DBDCA7}" name="Tabla84" displayName="Tabla84" ref="A1:T6" totalsRowShown="0" headerRowDxfId="63">
+  <autoFilter ref="A1:T6" xr:uid="{11AF62AA-310D-48FE-BA1B-7667C3DBDCA7}"/>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{7FA43690-F5EB-4E13-9A58-77BAB90416EE}" name="Procesos"/>
+    <tableColumn id="6" xr3:uid="{3A89EFDD-17C0-4B54-957C-0FB52980B7A3}" name="Líder"/>
+    <tableColumn id="15" xr3:uid="{C0D29E03-98F1-416D-A2E5-131F3BEE4DBF}" name="¿Contenido dentro de una iniciativa?" dataDxfId="62"/>
+    <tableColumn id="19" xr3:uid="{47B3B8AD-4B8C-4C6D-BCC7-59727929E1A4}" name="Fecha Iniciativa" dataDxfId="61"/>
+    <tableColumn id="2" xr3:uid="{B2387C4F-5517-485B-95EB-0E5682BCFF4F}" name="Status del proceso" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{33557364-A07A-43F2-B9D5-50D87CC9B584}" name="Complejidad" dataDxfId="59">
+      <calculatedColumnFormula>Tabla4[[#This Row],[Puntaje Final (1-10)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{B515DA5E-9024-4A84-9E3E-200AE8C34D77}" name="To-be" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{69145EA3-07F3-466C-8301-64DBA9013D74}" name="As-is" dataDxfId="57"/>
+    <tableColumn id="5" xr3:uid="{15205F52-713C-4013-928A-E256171033FA}" name="Notas" dataDxfId="56"/>
+    <tableColumn id="14" xr3:uid="{FAD82E3E-F21A-49A8-828D-964A9BF62134}" name="Levantar información" dataDxfId="55"/>
+    <tableColumn id="13" xr3:uid="{F8EA1DDC-874A-4E16-8657-C5CF9979654B}" name="Armar diagrama" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{FAA1E2CD-B097-4C74-8452-0DE0D7CADB1B}" name="Validar diagrama" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{A2BB0178-D23F-4179-A0B4-0F8F082A21EC}" name="Mejorar proceso" dataDxfId="52"/>
+    <tableColumn id="9" xr3:uid="{EBC42DD4-CA09-42D7-875D-C7B836DAE820}" name="Validar mejora" dataDxfId="51"/>
+    <tableColumn id="12" xr3:uid="{FA384004-9376-4186-BC5E-AFD808EE03B1}" name="Implementación" dataDxfId="50"/>
+    <tableColumn id="16" xr3:uid="{D7F47828-C923-49B4-932F-3DB282948A1A}" name="% de avance" dataDxfId="49" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula array="1">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="20" xr3:uid="{8DF0493C-09A5-43BB-A83A-1C98E2FF5170}" name="Fecha Inicio" dataDxfId="48" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{DD10AE7F-0B7F-4F4B-A4D5-8CFBFE66E665}" name="Tiempo bruto de levantamiento " dataDxfId="47">
+      <calculatedColumnFormula>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{BD00BC4D-A4D2-412C-B776-527EE547F3EC}" name="Tiempo especifico en semanas" dataDxfId="46">
+      <calculatedColumnFormula>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{6DEBBB95-676A-499F-8140-11974486632D}" name="Tiempo en meses" dataDxfId="45">
+      <calculatedColumnFormula>(6.5 + (F2 - 1) * 0.9444) / 4.345</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B71FA8F6-2F96-4D6F-BEBD-C09F4167A1E7}" name="Tabla35" displayName="Tabla35" ref="J10:N17" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" headerRowBorderDxfId="41" tableBorderDxfId="42" totalsRowBorderDxfId="40">
+  <autoFilter ref="J10:N17" xr:uid="{B71FA8F6-2F96-4D6F-BEBD-C09F4167A1E7}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{E5E47028-4EB2-47E1-A331-EF8793193E4B}" name="Columna" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{DC99D347-F09A-479C-B803-5B418CBC48F2}" name="Celda" dataDxfId="38"/>
+    <tableColumn id="3" xr3:uid="{66A59C75-60FC-4A2D-BA85-3D09A690AD13}" name="Promedio" dataDxfId="37"/>
+    <tableColumn id="4" xr3:uid="{0B44A7A1-1887-4359-BF73-914FF1126694}" name="Peso (%)" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{E5EDC793-95B4-46D2-B220-2B6353EC5DD4}" name="Factor Decimal" dataDxfId="35"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}" name="Tabla8" displayName="Tabla8" ref="A1:T6" totalsRowShown="0" headerRowDxfId="119">
+  <autoFilter ref="A1:T6" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}"/>
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{9D6B40D3-3215-4E98-A9FC-D478FB63C1BA}" name="Procesos"/>
+    <tableColumn id="6" xr3:uid="{F5B3BD05-8E49-49F1-93DE-92D27F1C49E6}" name="Líder"/>
+    <tableColumn id="15" xr3:uid="{1EA989C9-73CA-4A22-B626-AC262B041ED9}" name="¿Contenido dentro de una iniciativa?" dataDxfId="118"/>
+    <tableColumn id="19" xr3:uid="{C9D6E896-9CBC-4057-9F81-12423CB4D99E}" name="Fecha Iniciativa" dataDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{EEDD7810-0171-43A9-9288-43A6DF88CC68}" name="Status del proceso" dataDxfId="116"/>
+    <tableColumn id="3" xr3:uid="{234448FA-6E6F-424A-931A-3653E7178265}" name="Complejidad" dataDxfId="115">
+      <calculatedColumnFormula>Tabla4[[#This Row],[Puntaje Final (1-10)]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{5A4FFE81-7563-4F38-8BE5-EA30FC7C196D}" name="To-be" dataDxfId="114"/>
+    <tableColumn id="11" xr3:uid="{35D54FDE-D4BF-4FD2-9479-B2182C98B6D5}" name="As-is" dataDxfId="113"/>
+    <tableColumn id="5" xr3:uid="{E6EB2333-E84F-41CE-8EAC-52D77BF66F44}" name="Notas" dataDxfId="112"/>
+    <tableColumn id="14" xr3:uid="{8112EDF6-BC89-4919-A355-D2D3D1BF34BA}" name="Levantar información" dataDxfId="111"/>
+    <tableColumn id="13" xr3:uid="{2EA9FA24-C3F1-4C14-A867-A6FAC65E747C}" name="Armar diagrama" dataDxfId="110"/>
+    <tableColumn id="8" xr3:uid="{CD6D287B-BCEC-45D9-8EB8-A0F76A9F8CAF}" name="Validar diagrama" dataDxfId="109"/>
+    <tableColumn id="7" xr3:uid="{F4FF766B-5291-4082-A0FF-A66586E7C142}" name="Mejorar proceso" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{0C5A0591-A510-455E-AD87-7F86245A682D}" name="Validar mejora" dataDxfId="107"/>
+    <tableColumn id="12" xr3:uid="{C63E8C68-557E-49A9-8D27-236FDCB340BC}" name="Implementación" dataDxfId="106"/>
+    <tableColumn id="16" xr3:uid="{8B4C9571-AFDF-4088-806A-0420B7E2442E}" name="% de avance" dataDxfId="105" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula array="1">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="20" xr3:uid="{7CE675F8-BCC9-4D91-AE6F-A7A6A1C260DD}" name="Fecha Inicio" dataDxfId="104" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{B6DD48A4-1AB9-4C6E-A7E2-D52D8502F05C}" name="Tiempo bruto de levantamiento " dataDxfId="103">
+      <calculatedColumnFormula>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="17" xr3:uid="{97833884-FD4C-49EA-8567-FE1DD15B1ED4}" name="Tiempo especifico en semanas" dataDxfId="102">
+      <calculatedColumnFormula>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="18" xr3:uid="{79F26D04-CE30-49F5-B63D-964F30F64CC4}" name="Tiempo en meses" dataDxfId="101">
+      <calculatedColumnFormula>(6.5 + (F2 - 1) * 0.9444) / 4.345</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}" name="Tabla3" displayName="Tabla3" ref="J10:N17" totalsRowShown="0" headerRowDxfId="100" dataDxfId="98" headerRowBorderDxfId="99" tableBorderDxfId="97" totalsRowBorderDxfId="96">
+  <autoFilter ref="J10:N17" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{22A678DC-4FD4-457E-BF2F-A5B26AF5A9EF}" name="Columna" dataDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{20414C72-C442-4898-9B74-EA7858B03946}" name="Celda" dataDxfId="94"/>
+    <tableColumn id="3" xr3:uid="{BA1EDFE7-FD4C-4A18-B24F-51500610B0F3}" name="Promedio" dataDxfId="93"/>
+    <tableColumn id="4" xr3:uid="{18E92589-EFEA-448D-8CFF-7A861810DB8E}" name="Peso (%)" dataDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{D9FEA8B4-A59E-4AC5-9FA6-A99F7AA97E09}" name="Factor Decimal" dataDxfId="91"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4FD466F-89DF-47BA-AC9E-559F47CB9595}" name="Tabla4" displayName="Tabla4" ref="A1:H6" totalsRowShown="0" headerRowDxfId="90">
   <autoFilter ref="A1:H6" xr:uid="{A4FD466F-89DF-47BA-AC9E-559F47CB9595}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{209BC8CE-A4E5-4EAD-9176-25919D421EE7}" name="Proceso" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{AD141033-AAC8-430E-AED3-EE13742AEDEF}" name="Áreas Involucradas (25%)" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{81BAF825-E86C-4EAB-83B0-4BEF6E690DAF}" name="Contenido dentro de una iniciativa (20%)" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{BD9A8428-D2BF-47C3-8A4D-000DDA7085B1}" name="¿Requiere desarrollo tecnologico? (20%)" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{CC386173-731D-4092-A2CC-5DFC807607AC}" name="¿Es un levantamiento nuevo? (15%)" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{44DB2B51-5EBC-435E-B533-35DBC727260D}" name="¿Toca un proceso clave? (20%)" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{91CAEE15-D755-4AEE-BD7E-76CF718F3FEF}" name="Puntaje Final (1-10)" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{209BC8CE-A4E5-4EAD-9176-25919D421EE7}" name="Proceso" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{AD141033-AAC8-430E-AED3-EE13742AEDEF}" name="Áreas Involucradas (25%)" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{81BAF825-E86C-4EAB-83B0-4BEF6E690DAF}" name="Contenido dentro de una iniciativa (20%)" dataDxfId="87"/>
+    <tableColumn id="5" xr3:uid="{BD9A8428-D2BF-47C3-8A4D-000DDA7085B1}" name="¿Requiere desarrollo tecnologico? (20%)" dataDxfId="86"/>
+    <tableColumn id="6" xr3:uid="{CC386173-731D-4092-A2CC-5DFC807607AC}" name="¿Es un levantamiento nuevo? (15%)" dataDxfId="85"/>
+    <tableColumn id="7" xr3:uid="{44DB2B51-5EBC-435E-B533-35DBC727260D}" name="¿Toca un proceso clave? (20%)" dataDxfId="84"/>
+    <tableColumn id="8" xr3:uid="{91CAEE15-D755-4AEE-BD7E-76CF718F3FEF}" name="Puntaje Final (1-10)" dataDxfId="83">
       <calculatedColumnFormula>IF(B2="", "", 10 * ( (MATCH(B2, {"1-2";"3-4";"4+"}, 0)/3)*0.25 + N(C2)*0.2 + N(D2)*0.2 + N(E2)*0.15 + N(F2)*0.2 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{83E13230-22E5-49E0-9B92-C34352FB3731}" name="Complejidad" dataDxfId="19">
+    <tableColumn id="4" xr3:uid="{83E13230-22E5-49E0-9B92-C34352FB3731}" name="Complejidad" dataDxfId="82">
       <calculatedColumnFormula>+IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&lt;=4,"Baja",IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&gt;7,"Alta","Media"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2645,29 +5679,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AED4591-DDAA-4945-939F-A4AF72524E54}">
-  <dimension ref="A1:T46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="30.54296875" customWidth="1"/>
-    <col min="2" max="2" width="38.7265625" customWidth="1"/>
-    <col min="3" max="3" width="45.81640625" customWidth="1"/>
-    <col min="4" max="4" width="32.453125" style="40" customWidth="1"/>
-    <col min="5" max="5" width="23.26953125" customWidth="1"/>
-    <col min="6" max="6" width="22.7265625" customWidth="1"/>
-    <col min="7" max="7" width="24.81640625" customWidth="1"/>
-    <col min="8" max="8" width="22.1796875" customWidth="1"/>
-    <col min="9" max="9" width="55.81640625" customWidth="1"/>
-    <col min="10" max="11" width="22.7265625" customWidth="1"/>
-    <col min="12" max="14" width="24.1796875" customWidth="1"/>
-    <col min="15" max="16" width="22.7265625" customWidth="1"/>
-    <col min="17" max="17" width="27.81640625" style="40" customWidth="1"/>
-    <col min="18" max="18" width="32" customWidth="1"/>
-    <col min="19" max="19" width="30.453125" customWidth="1"/>
-    <col min="20" max="20" width="29.453125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E96A1914-BFA8-48BA-9F36-5CD0C57C9F17}">
+  <dimension ref="A1:T41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:20" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2729,7 +5745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -2789,7 +5805,7 @@
         <v>3.1261219792865367</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -2849,7 +5865,7 @@
         <v>2.6914154200230151</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
         <v>22</v>
       </c>
@@ -2909,7 +5925,7 @@
         <v>2.5827387802071349</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2969,7 +5985,7 @@
         <v>1.8220023014959725</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -3036,13 +6052,15 @@
       <c r="E7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q7" s="40"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C8" s="13"/>
       <c r="D8" s="39"/>
       <c r="E8" s="13"/>
       <c r="G8" s="13"/>
       <c r="H8" s="13"/>
+      <c r="Q8" s="40"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C9" s="13"/>
@@ -3052,6 +6070,7 @@
       <c r="G9" s="13"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
+      <c r="Q9" s="40"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C10" s="13"/>
@@ -3077,6 +6096,1695 @@
       <c r="N10" s="28" t="s">
         <v>30</v>
       </c>
+      <c r="Q10" s="40"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="D11" s="40"/>
+      <c r="E11" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="29">
+        <v>2</v>
+      </c>
+      <c r="M11" s="30">
+        <v>0.1875</v>
+      </c>
+      <c r="N11" s="11">
+        <v>0.1875</v>
+      </c>
+      <c r="P11" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="44">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="D12" s="40"/>
+      <c r="E12" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="29">
+        <v>0.67</v>
+      </c>
+      <c r="M12" s="30">
+        <v>6.25E-2</v>
+      </c>
+      <c r="N12" s="11">
+        <v>6.25E-2</v>
+      </c>
+      <c r="P12" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q12" s="45">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B13" s="4"/>
+      <c r="D13" s="40"/>
+      <c r="F13" s="34"/>
+      <c r="J13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="M13" s="30">
+        <v>0.1406</v>
+      </c>
+      <c r="N13" s="11">
+        <v>0.1406</v>
+      </c>
+      <c r="P13" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="44">
+        <v>0.1406</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B14" s="4"/>
+      <c r="D14" s="40"/>
+      <c r="F14" s="33"/>
+      <c r="J14" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" s="29">
+        <v>4</v>
+      </c>
+      <c r="M14" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="N14" s="11">
+        <v>0.375</v>
+      </c>
+      <c r="P14" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q14" s="45">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B15" s="4"/>
+      <c r="D15" s="40"/>
+      <c r="J15" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L15" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="M15" s="30">
+        <v>0.1406</v>
+      </c>
+      <c r="N15" s="11">
+        <v>0.1406</v>
+      </c>
+      <c r="P15" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="44">
+        <v>0.1406</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B16" s="4"/>
+      <c r="D16" s="40"/>
+      <c r="J16" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="29">
+        <v>1</v>
+      </c>
+      <c r="M16" s="30">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="N16" s="11">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="P16" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="45">
+        <v>9.3799999999999994E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B17" s="4"/>
+      <c r="D17" s="40"/>
+      <c r="J17" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="K17" s="32"/>
+      <c r="L17" s="9">
+        <v>10.67</v>
+      </c>
+      <c r="M17" s="10">
+        <v>1</v>
+      </c>
+      <c r="N17" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="40"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B18" s="4"/>
+      <c r="D18" s="40"/>
+      <c r="Q18" s="40"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B19" s="4"/>
+      <c r="D19" s="40"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="D20" s="40"/>
+      <c r="N20" s="24"/>
+      <c r="Q20" s="40"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B21" s="4"/>
+      <c r="D21" s="40"/>
+      <c r="N21" s="24"/>
+      <c r="Q21" s="40"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B22" s="4"/>
+      <c r="D22" s="40"/>
+      <c r="N22" s="24"/>
+      <c r="Q22" s="40"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B23" s="4"/>
+      <c r="D23" s="40"/>
+      <c r="N23" s="24"/>
+      <c r="Q23" s="40"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B24" s="4"/>
+      <c r="D24" s="40"/>
+      <c r="N24" s="24"/>
+      <c r="Q24" s="40"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B25" s="4"/>
+      <c r="D25" s="40"/>
+      <c r="N25" s="24"/>
+      <c r="Q25" s="40"/>
+      <c r="R25" s="33"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B26" s="4"/>
+      <c r="D26" s="40"/>
+      <c r="Q26" s="40"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B27" s="4"/>
+      <c r="D27" s="40"/>
+      <c r="Q27" s="40"/>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D28" s="40"/>
+      <c r="Q28" s="40"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D29" s="40"/>
+      <c r="Q29" s="40"/>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D30" s="40"/>
+      <c r="Q30" s="40"/>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D31" s="40"/>
+      <c r="Q31" s="40"/>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D32" s="40"/>
+      <c r="Q32" s="40"/>
+    </row>
+    <row r="33" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D33" s="40"/>
+      <c r="Q33" s="40"/>
+    </row>
+    <row r="34" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D34" s="40"/>
+      <c r="Q34" s="40"/>
+    </row>
+    <row r="35" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D35" s="40"/>
+      <c r="Q35" s="40"/>
+    </row>
+    <row r="36" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D36" s="40"/>
+      <c r="Q36" s="40"/>
+    </row>
+    <row r="37" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D37" s="40"/>
+      <c r="Q37" s="40"/>
+    </row>
+    <row r="38" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D38" s="40"/>
+      <c r="Q38" s="40"/>
+    </row>
+    <row r="39" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D39" s="40"/>
+      <c r="Q39" s="40"/>
+    </row>
+    <row r="40" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D40" s="40"/>
+      <c r="Q40" s="40"/>
+    </row>
+    <row r="41" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D41" s="40"/>
+      <c r="Q41" s="40"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:D6">
+    <cfRule type="expression" dxfId="34" priority="6">
+      <formula>$H2=TRUE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="33" priority="7">
+      <formula>$G2=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="8">
+      <formula>$G2=TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E6 E13:E41">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
+      <formula>"Listo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
+      <formula>"No iniciado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
+      <formula>"En curso"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R6">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:S6">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S6">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T6 R2:R6">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{9EF8EA59-F559-43BF-A368-A6700DA2832D}">
+      <formula1>"No iniciado,En curso,Listo"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05CDFC9F-E2B1-4FD0-B740-E450CA39F138}">
+  <dimension ref="A1:T41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="38"/>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>8.5</v>
+      </c>
+      <c r="G2" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="25" cm="1">
+        <f t="array" ref="P2">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.76560000000000006</v>
+      </c>
+      <c r="Q2" s="41">
+        <v>45992</v>
+      </c>
+      <c r="R2" s="3">
+        <f>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</f>
+        <v>15</v>
+      </c>
+      <c r="S2" s="6">
+        <f>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>13.583333333333332</v>
+      </c>
+      <c r="T2" s="6">
+        <f>(6.5 + (F2 - 1) * 0.9444) / 4.345</f>
+        <v>3.1261219792865367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="38"/>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>6.5</v>
+      </c>
+      <c r="G3" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="25" cm="1">
+        <f t="array" ref="P3">+SUMPRODUCT(--(J3:O3),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.3906</v>
+      </c>
+      <c r="Q3" s="41">
+        <v>45999</v>
+      </c>
+      <c r="R3" s="3">
+        <f>IF(F3&lt;=3, 6.5, IF(F3&lt;=7, 10.5, 15))</f>
+        <v>10.5</v>
+      </c>
+      <c r="S3" s="6">
+        <f>6.5 + (F3 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>11.694444444444445</v>
+      </c>
+      <c r="T3" s="6">
+        <f>(6.5 + (F3 - 1) * 0.9444) / 4.345</f>
+        <v>2.6914154200230151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A4" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="38"/>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>6.0000000000000009</v>
+      </c>
+      <c r="G4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="25" cm="1">
+        <f t="array" ref="P4">+SUMPRODUCT(--(J4:O4),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.3906</v>
+      </c>
+      <c r="Q4" s="41">
+        <v>46006</v>
+      </c>
+      <c r="R4" s="3">
+        <f>IF(F4&lt;=3, 6.5, IF(F4&lt;=7, 10.5, 15))</f>
+        <v>10.5</v>
+      </c>
+      <c r="S4" s="6">
+        <f>6.5 + (F4 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>11.222222222222223</v>
+      </c>
+      <c r="T4" s="6">
+        <f>(6.5 + (F4 - 1) * 0.9444) / 4.345</f>
+        <v>2.5827387802071349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="38"/>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>2.5</v>
+      </c>
+      <c r="G5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="25" cm="1">
+        <f t="array" ref="P5">+SUMPRODUCT(--(J5:O5),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>46027</v>
+      </c>
+      <c r="R5" s="3">
+        <f>IF(F5&lt;=3, 6.5, IF(F5&lt;=7, 10.5, 15))</f>
+        <v>6.5</v>
+      </c>
+      <c r="S5" s="6">
+        <f>6.5 + (F5 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>7.9166666666666661</v>
+      </c>
+      <c r="T5" s="6">
+        <f>(6.5 + (F5 - 1) * 0.9444) / 4.345</f>
+        <v>1.8220023014959725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="38"/>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>4.5</v>
+      </c>
+      <c r="G6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="25" cm="1">
+        <f t="array" ref="P6">+SUMPRODUCT(--(J6:O6),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.1875</v>
+      </c>
+      <c r="Q6" s="41">
+        <v>46048</v>
+      </c>
+      <c r="R6" s="3">
+        <f>IF(F6&lt;=3, 6.5, IF(F6&lt;=7, 10.5, 15))</f>
+        <v>10.5</v>
+      </c>
+      <c r="S6" s="6">
+        <f>6.5 + (F6 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>9.8055555555555554</v>
+      </c>
+      <c r="T6" s="6">
+        <f>(6.5 + (F6 - 1) * 0.9444) / 4.345</f>
+        <v>2.2567088607594941</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C7" s="13"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="Q7" s="40"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C8" s="13"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="Q8" s="40"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C9" s="13"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="Q9" s="40"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C10" s="13"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="40"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="D11" s="40"/>
+      <c r="E11" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="29">
+        <v>2</v>
+      </c>
+      <c r="M11" s="30">
+        <v>0.1875</v>
+      </c>
+      <c r="N11" s="11">
+        <v>0.1875</v>
+      </c>
+      <c r="P11" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="44">
+        <v>0.1875</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="D12" s="40"/>
+      <c r="E12" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="29">
+        <v>0.67</v>
+      </c>
+      <c r="M12" s="30">
+        <v>6.25E-2</v>
+      </c>
+      <c r="N12" s="11">
+        <v>6.25E-2</v>
+      </c>
+      <c r="P12" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q12" s="45">
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B13" s="4"/>
+      <c r="D13" s="40"/>
+      <c r="F13" s="34"/>
+      <c r="J13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="M13" s="30">
+        <v>0.1406</v>
+      </c>
+      <c r="N13" s="11">
+        <v>0.1406</v>
+      </c>
+      <c r="P13" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="44">
+        <v>0.1406</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B14" s="4"/>
+      <c r="D14" s="40"/>
+      <c r="F14" s="33"/>
+      <c r="J14" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" s="29">
+        <v>4</v>
+      </c>
+      <c r="M14" s="30">
+        <v>0.375</v>
+      </c>
+      <c r="N14" s="11">
+        <v>0.375</v>
+      </c>
+      <c r="P14" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q14" s="45">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B15" s="4"/>
+      <c r="D15" s="40"/>
+      <c r="J15" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L15" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="M15" s="30">
+        <v>0.1406</v>
+      </c>
+      <c r="N15" s="11">
+        <v>0.1406</v>
+      </c>
+      <c r="P15" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="44">
+        <v>0.1406</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B16" s="4"/>
+      <c r="D16" s="40"/>
+      <c r="J16" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="L16" s="29">
+        <v>1</v>
+      </c>
+      <c r="M16" s="30">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="N16" s="11">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="P16" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="45">
+        <v>9.3799999999999994E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B17" s="4"/>
+      <c r="D17" s="40"/>
+      <c r="J17" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="K17" s="32"/>
+      <c r="L17" s="9">
+        <v>10.67</v>
+      </c>
+      <c r="M17" s="10">
+        <v>1</v>
+      </c>
+      <c r="N17" s="11">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="40"/>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B18" s="4"/>
+      <c r="D18" s="40"/>
+      <c r="Q18" s="40"/>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B19" s="4"/>
+      <c r="D19" s="40"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B20" s="4"/>
+      <c r="D20" s="40"/>
+      <c r="N20" s="24"/>
+      <c r="Q20" s="40"/>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B21" s="4"/>
+      <c r="D21" s="40"/>
+      <c r="N21" s="24"/>
+      <c r="Q21" s="40"/>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B22" s="4"/>
+      <c r="D22" s="40"/>
+      <c r="N22" s="24"/>
+      <c r="Q22" s="40"/>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B23" s="4"/>
+      <c r="D23" s="40"/>
+      <c r="N23" s="24"/>
+      <c r="Q23" s="40"/>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B24" s="4"/>
+      <c r="D24" s="40"/>
+      <c r="N24" s="24"/>
+      <c r="Q24" s="40"/>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B25" s="4"/>
+      <c r="D25" s="40"/>
+      <c r="N25" s="24"/>
+      <c r="Q25" s="40"/>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B26" s="4"/>
+      <c r="D26" s="40"/>
+      <c r="Q26" s="40"/>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="B27" s="4"/>
+      <c r="D27" s="40"/>
+      <c r="Q27" s="40"/>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D28" s="40"/>
+      <c r="Q28" s="40"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D29" s="40"/>
+      <c r="Q29" s="40"/>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D30" s="40"/>
+      <c r="Q30" s="40"/>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D31" s="40"/>
+      <c r="Q31" s="40"/>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="D32" s="40"/>
+      <c r="Q32" s="40"/>
+    </row>
+    <row r="33" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D33" s="40"/>
+      <c r="Q33" s="40"/>
+    </row>
+    <row r="34" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D34" s="40"/>
+      <c r="Q34" s="40"/>
+    </row>
+    <row r="35" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D35" s="40"/>
+      <c r="Q35" s="40"/>
+    </row>
+    <row r="36" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D36" s="40"/>
+      <c r="Q36" s="40"/>
+    </row>
+    <row r="37" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D37" s="40"/>
+      <c r="Q37" s="40"/>
+    </row>
+    <row r="38" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D38" s="40"/>
+      <c r="Q38" s="40"/>
+    </row>
+    <row r="39" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D39" s="40"/>
+      <c r="Q39" s="40"/>
+    </row>
+    <row r="40" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D40" s="40"/>
+      <c r="Q40" s="40"/>
+    </row>
+    <row r="41" spans="4:17" x14ac:dyDescent="0.35">
+      <c r="D41" s="40"/>
+      <c r="Q41" s="40"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:D6">
+    <cfRule type="expression" dxfId="69" priority="6">
+      <formula>$H2=TRUE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="7">
+      <formula>$G2=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="8">
+      <formula>$G2=TRUE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E6 E13:E41">
+    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+      <formula>"Listo"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="65" priority="4" operator="equal">
+      <formula>"No iniciado"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="64" priority="5" operator="equal">
+      <formula>"En curso"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:R6">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R2:S6">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S6">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T6 R2:R6">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T6">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{BF64BDE7-CBAB-4F78-81B2-E23F87FF287C}">
+      <formula1>"No iniciado,En curso,Listo"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AED4591-DDAA-4945-939F-A4AF72524E54}">
+  <dimension ref="A1:T46"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="10.90625" customWidth="1"/>
+    <col min="4" max="4" width="10.90625" style="40" customWidth="1"/>
+    <col min="5" max="16" width="10.90625" customWidth="1"/>
+    <col min="17" max="17" width="10.90625" style="40" customWidth="1"/>
+    <col min="18" max="20" width="10.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D2" s="38"/>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>8.5</v>
+      </c>
+      <c r="G2" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H2" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2" s="25" cm="1">
+        <f t="array" ref="P2">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.76560000000000006</v>
+      </c>
+      <c r="Q2" s="41">
+        <v>45992</v>
+      </c>
+      <c r="R2" s="3">
+        <f>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</f>
+        <v>15</v>
+      </c>
+      <c r="S2" s="6">
+        <f>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>13.583333333333332</v>
+      </c>
+      <c r="T2" s="6">
+        <f>(6.5 + (F2 - 1) * 0.9444) / 4.345</f>
+        <v>3.1261219792865367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D3" s="38"/>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>6.5</v>
+      </c>
+      <c r="G3" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H3" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P3" s="25" cm="1">
+        <f t="array" ref="P3">+SUMPRODUCT(--(J3:O3),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.3906</v>
+      </c>
+      <c r="Q3" s="41">
+        <v>45999</v>
+      </c>
+      <c r="R3" s="3">
+        <f>IF(F3&lt;=3, 6.5, IF(F3&lt;=7, 10.5, 15))</f>
+        <v>10.5</v>
+      </c>
+      <c r="S3" s="6">
+        <f>6.5 + (F3 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>11.694444444444445</v>
+      </c>
+      <c r="T3" s="6">
+        <f>(6.5 + (F3 - 1) * 0.9444) / 4.345</f>
+        <v>2.6914154200230151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" s="38"/>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>6.0000000000000009</v>
+      </c>
+      <c r="G4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P4" s="25" cm="1">
+        <f t="array" ref="P4">+SUMPRODUCT(--(J4:O4),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.3906</v>
+      </c>
+      <c r="Q4" s="41">
+        <v>46006</v>
+      </c>
+      <c r="R4" s="3">
+        <f>IF(F4&lt;=3, 6.5, IF(F4&lt;=7, 10.5, 15))</f>
+        <v>10.5</v>
+      </c>
+      <c r="S4" s="6">
+        <f>6.5 + (F4 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>11.222222222222223</v>
+      </c>
+      <c r="T4" s="6">
+        <f>(6.5 + (F4 - 1) * 0.9444) / 4.345</f>
+        <v>2.5827387802071349</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="38"/>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>2.5</v>
+      </c>
+      <c r="G5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P5" s="25" cm="1">
+        <f t="array" ref="P5">+SUMPRODUCT(--(J5:O5),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.53120000000000001</v>
+      </c>
+      <c r="Q5" s="41">
+        <v>46027</v>
+      </c>
+      <c r="R5" s="3">
+        <f>IF(F5&lt;=3, 6.5, IF(F5&lt;=7, 10.5, 15))</f>
+        <v>6.5</v>
+      </c>
+      <c r="S5" s="6">
+        <f>6.5 + (F5 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>7.9166666666666661</v>
+      </c>
+      <c r="T5" s="6">
+        <f>(6.5 + (F5 - 1) * 0.9444) / 4.345</f>
+        <v>1.8220023014959725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" s="38"/>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="16">
+        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
+        <v>4.5</v>
+      </c>
+      <c r="G6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6" s="25" cm="1">
+        <f t="array" ref="P6">+SUMPRODUCT(--(J6:O6),TRANSPOSE($N$11:$N$16))</f>
+        <v>0.1875</v>
+      </c>
+      <c r="Q6" s="41">
+        <v>46048</v>
+      </c>
+      <c r="R6" s="3">
+        <f>IF(F6&lt;=3, 6.5, IF(F6&lt;=7, 10.5, 15))</f>
+        <v>10.5</v>
+      </c>
+      <c r="S6" s="6">
+        <f>6.5 + (F6 - 1) * ((15 - 6.5) / (10 - 1))</f>
+        <v>9.8055555555555554</v>
+      </c>
+      <c r="T6" s="6">
+        <f>(6.5 + (F6 - 1) * 0.9444) / 4.345</f>
+        <v>2.2567088607594941</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C7" s="13"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="13"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C9" s="13"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="C10" s="13"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" s="28" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="E11" s="17" t="s">
@@ -3098,6 +7806,12 @@
       <c r="N11" s="11">
         <v>0.1875</v>
       </c>
+      <c r="P11" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="44">
+        <v>0.1875</v>
+      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="E12" s="18" t="s">
@@ -3116,6 +7830,12 @@
         <v>6.25E-2</v>
       </c>
       <c r="N12" s="11">
+        <v>6.25E-2</v>
+      </c>
+      <c r="P12" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q12" s="45">
         <v>6.25E-2</v>
       </c>
     </row>
@@ -3137,6 +7857,12 @@
       <c r="N13" s="11">
         <v>0.1406</v>
       </c>
+      <c r="P13" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q13" s="44">
+        <v>0.1406</v>
+      </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B14" s="4"/>
@@ -3156,6 +7882,12 @@
       <c r="N14" s="11">
         <v>0.375</v>
       </c>
+      <c r="P14" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q14" s="45">
+        <v>0.375</v>
+      </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B15" s="4"/>
@@ -3174,6 +7906,12 @@
       <c r="N15" s="11">
         <v>0.1406</v>
       </c>
+      <c r="P15" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q15" s="44">
+        <v>0.1406</v>
+      </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B16" s="4"/>
@@ -3190,6 +7928,12 @@
         <v>9.3799999999999994E-2</v>
       </c>
       <c r="N16" s="11">
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="P16" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q16" s="45">
         <v>9.3799999999999994E-2</v>
       </c>
     </row>
@@ -3256,24 +8000,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:D6">
-    <cfRule type="expression" dxfId="18" priority="23">
+    <cfRule type="expression" dxfId="81" priority="23">
       <formula>$H2=TRUE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="24">
+    <cfRule type="expression" dxfId="80" priority="24">
       <formula>$G2=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="16" priority="25">
+    <cfRule type="expression" dxfId="79" priority="25">
       <formula>$G2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E6 E13:E1048576">
-    <cfRule type="cellIs" dxfId="15" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="8" operator="equal">
       <formula>"Listo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="9" operator="equal">
       <formula>"No iniciado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="10" operator="equal">
       <formula>"En curso"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3384,7 +8128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6139A592-A579-4963-915C-84924787727F}">
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3592,24 +8336,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A6">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="75" priority="1">
       <formula>$H2=TRUE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="2">
+    <cfRule type="expression" dxfId="74" priority="2">
       <formula>$G2=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="3">
+    <cfRule type="expression" dxfId="73" priority="3">
       <formula>$G2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="7" operator="equal">
       <formula>"Listo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="8" operator="equal">
       <formula>"No iniciado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="9" operator="equal">
       <formula>"En curso"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Procesos_Grafico.xlsx
+++ b/Procesos_Grafico.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l_moya\Downloads\python_analisis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D95113BC-3F3F-40E8-9C8A-4737CD0F6397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920F29E2-8D21-4756-B77D-8FC9D9C1F4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2200" yWindow="2200" windowWidth="14400" windowHeight="7270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envasado" sheetId="9" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="64">
   <si>
     <t>Procesos</t>
   </si>
@@ -232,6 +232,27 @@
   </si>
   <si>
     <t>Fecha Inicio</t>
+  </si>
+  <si>
+    <t>Cilindro defectuoso y poca duración.</t>
+  </si>
+  <si>
+    <t>Pago Digital / Reembolso y devolución</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proceso de reembolso y devolución de dinero (pago digital) </t>
+  </si>
+  <si>
+    <t>Flujo del viaje del chofer</t>
+  </si>
+  <si>
+    <t>Devolucion de cilindro DI</t>
+  </si>
+  <si>
+    <t>Corte y reposición</t>
+  </si>
+  <si>
+    <t>Autolectura</t>
   </si>
 </sst>
 </file>
@@ -617,413 +638,63 @@
   <dxfs count="120">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[&lt;4]&quot;Baja: &quot;0.0;[&lt;7]&quot;Media: &quot;0.0;&quot;Alta: &quot;0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color rgb="FF4D2200"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF542E00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1087,413 +758,63 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-0.14999847407452621"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="[&lt;4]&quot;Baja: &quot;0.0;[&lt;7]&quot;Media: &quot;0.0;&quot;Alta: &quot;0.0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <color rgb="FF4D2200"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF542E00"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1556,127 +877,21 @@
       </fill>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
       <font>
-        <color rgb="FF4D2200"/>
+        <b/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF542E00"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF4D2200"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF542E00"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
           <xfpb:DXFComplement i="1"/>
@@ -1684,37 +899,23 @@
       </extLst>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
@@ -2064,42 +1265,42 @@
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
     <dxf>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
@@ -2116,7 +1317,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
@@ -2130,7 +1331,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
@@ -2181,7 +1382,827 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[&lt;4]&quot;Baja: &quot;0.0;[&lt;7]&quot;Media: &quot;0.0;&quot;Alta: &quot;0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.14999847407452621"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="[&lt;4]&quot;Baja: &quot;0.0;[&lt;7]&quot;Media: &quot;0.0;&quot;Alta: &quot;0.0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="1"/>
         </ext>
       </extLst>
     </dxf>
@@ -5110,13 +5131,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>136523</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>92528</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>1490435</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>115207</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5208,45 +5229,45 @@
   </bag>
   <bag type="DXFComplements" extRef="DXFComplementsMapperExtRef">
     <a k="MappedFeaturePropertyBags">
+      <bagId>5</bagId>
       <bagId>2</bagId>
-      <bagId>5</bagId>
     </a>
   </bag>
 </FeaturePropertyBags>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{10537967-845A-432A-A796-359783753A79}" name="Tabla86" displayName="Tabla86" ref="A1:T6" totalsRowShown="0" headerRowDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{10537967-845A-432A-A796-359783753A79}" name="Tabla86" displayName="Tabla86" ref="A1:T6" totalsRowShown="0" headerRowDxfId="119">
   <autoFilter ref="A1:T6" xr:uid="{10537967-845A-432A-A796-359783753A79}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{6C5F92E5-C3C6-4D8E-A49F-6B0B4F47A477}" name="Procesos"/>
     <tableColumn id="6" xr3:uid="{A4A97957-CD05-4190-A7BC-FB5D702CCCF1}" name="Líder"/>
-    <tableColumn id="15" xr3:uid="{F530E09C-70F6-4AD4-9CE2-8799819B5F65}" name="¿Contenido dentro de una iniciativa?" dataDxfId="27"/>
-    <tableColumn id="19" xr3:uid="{3C563BB5-78D7-45A1-A12D-860D66970785}" name="Fecha Iniciativa" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{E521361E-8D00-4B07-BDC9-B96DE0FAAA03}" name="Status del proceso" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{D2819821-2057-4A7E-A310-4AC02854555C}" name="Complejidad" dataDxfId="24">
+    <tableColumn id="15" xr3:uid="{F530E09C-70F6-4AD4-9CE2-8799819B5F65}" name="¿Contenido dentro de una iniciativa?" dataDxfId="118"/>
+    <tableColumn id="19" xr3:uid="{3C563BB5-78D7-45A1-A12D-860D66970785}" name="Fecha Iniciativa" dataDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{E521361E-8D00-4B07-BDC9-B96DE0FAAA03}" name="Status del proceso" dataDxfId="116"/>
+    <tableColumn id="3" xr3:uid="{D2819821-2057-4A7E-A310-4AC02854555C}" name="Complejidad" dataDxfId="115">
       <calculatedColumnFormula>Tabla4[[#This Row],[Puntaje Final (1-10)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{910659FA-862C-418A-9007-D146C6B6B684}" name="To-be" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{9B51737A-8E09-4796-9384-789E3D581D12}" name="As-is" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{877AE1B5-D153-435F-B52E-B1481A61A124}" name="Notas" dataDxfId="21"/>
-    <tableColumn id="14" xr3:uid="{8DE3641F-379A-4221-9320-C93224F5AC4E}" name="Levantar información" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{DE691091-0924-4E9C-9FD6-3B0C1763FCB2}" name="Armar diagrama" dataDxfId="19"/>
-    <tableColumn id="8" xr3:uid="{5811FC46-4802-4991-847E-0BC4C8DE7412}" name="Validar diagrama" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{751291B1-2BE5-4977-BE55-88671D59C139}" name="Mejorar proceso" dataDxfId="17"/>
-    <tableColumn id="9" xr3:uid="{9D1BCA4F-9FA0-4C06-9B56-EFD6A64765CF}" name="Validar mejora" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{1F59F63E-CD23-4FCF-A4B9-69F9C655A4CF}" name="Implementación" dataDxfId="15"/>
-    <tableColumn id="16" xr3:uid="{74EBFE1F-7E13-4D16-9A55-DD551B786EE1}" name="% de avance" dataDxfId="14" dataCellStyle="Porcentaje">
+    <tableColumn id="4" xr3:uid="{910659FA-862C-418A-9007-D146C6B6B684}" name="To-be" dataDxfId="114"/>
+    <tableColumn id="11" xr3:uid="{9B51737A-8E09-4796-9384-789E3D581D12}" name="As-is" dataDxfId="113"/>
+    <tableColumn id="5" xr3:uid="{877AE1B5-D153-435F-B52E-B1481A61A124}" name="Notas" dataDxfId="112"/>
+    <tableColumn id="14" xr3:uid="{8DE3641F-379A-4221-9320-C93224F5AC4E}" name="Levantar información" dataDxfId="111"/>
+    <tableColumn id="13" xr3:uid="{DE691091-0924-4E9C-9FD6-3B0C1763FCB2}" name="Armar diagrama" dataDxfId="110"/>
+    <tableColumn id="8" xr3:uid="{5811FC46-4802-4991-847E-0BC4C8DE7412}" name="Validar diagrama" dataDxfId="109"/>
+    <tableColumn id="7" xr3:uid="{751291B1-2BE5-4977-BE55-88671D59C139}" name="Mejorar proceso" dataDxfId="108"/>
+    <tableColumn id="9" xr3:uid="{9D1BCA4F-9FA0-4C06-9B56-EFD6A64765CF}" name="Validar mejora" dataDxfId="107"/>
+    <tableColumn id="12" xr3:uid="{1F59F63E-CD23-4FCF-A4B9-69F9C655A4CF}" name="Implementación" dataDxfId="106"/>
+    <tableColumn id="16" xr3:uid="{74EBFE1F-7E13-4D16-9A55-DD551B786EE1}" name="% de avance" dataDxfId="105" dataCellStyle="Porcentaje">
       <calculatedColumnFormula array="1">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{337DB8B6-848F-4AFB-A923-18731D12D7EF}" name="Fecha Inicio" dataDxfId="13" dataCellStyle="Porcentaje"/>
-    <tableColumn id="10" xr3:uid="{D5F2AA22-FAE5-4AD9-A4A0-024DAA6378A6}" name="Tiempo bruto de levantamiento " dataDxfId="12">
+    <tableColumn id="20" xr3:uid="{337DB8B6-848F-4AFB-A923-18731D12D7EF}" name="Fecha Inicio" dataDxfId="104" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{D5F2AA22-FAE5-4AD9-A4A0-024DAA6378A6}" name="Tiempo bruto de levantamiento " dataDxfId="103">
       <calculatedColumnFormula>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{D61ADE36-BC70-4E92-B0A0-7B7DC901078C}" name="Tiempo especifico en semanas" dataDxfId="11">
+    <tableColumn id="17" xr3:uid="{D61ADE36-BC70-4E92-B0A0-7B7DC901078C}" name="Tiempo especifico en semanas" dataDxfId="102">
       <calculatedColumnFormula>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{23B9AFFA-2BB1-46FC-AE4C-6682319A6D47}" name="Tiempo en meses" dataDxfId="10">
+    <tableColumn id="18" xr3:uid="{23B9AFFA-2BB1-46FC-AE4C-6682319A6D47}" name="Tiempo en meses" dataDxfId="101">
       <calculatedColumnFormula>(6.5 + (F2 - 1) * 0.9444) / 4.345</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5255,51 +5276,51 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DE26E95-1ED7-42E2-B8D7-69FDD10E3622}" name="Tabla37" displayName="Tabla37" ref="J10:N17" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{1DE26E95-1ED7-42E2-B8D7-69FDD10E3622}" name="Tabla37" displayName="Tabla37" ref="J10:N17" totalsRowShown="0" headerRowDxfId="100" dataDxfId="98" headerRowBorderDxfId="99" tableBorderDxfId="97" totalsRowBorderDxfId="96">
   <autoFilter ref="J10:N17" xr:uid="{1DE26E95-1ED7-42E2-B8D7-69FDD10E3622}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{8CCFC06F-71F8-4178-88F3-5ABD60AE1EAE}" name="Columna" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{3F2EF7F8-BD08-4750-A577-7FD4B7C6664A}" name="Celda" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{971835D3-30F9-42D3-BEA1-520733792576}" name="Promedio" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{E2517CD1-8726-4109-92FB-1238481C74D3}" name="Peso (%)" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{A0A4FC88-C1B8-42FD-903E-A07CA6E46E3B}" name="Factor Decimal" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{8CCFC06F-71F8-4178-88F3-5ABD60AE1EAE}" name="Columna" dataDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{3F2EF7F8-BD08-4750-A577-7FD4B7C6664A}" name="Celda" dataDxfId="94"/>
+    <tableColumn id="3" xr3:uid="{971835D3-30F9-42D3-BEA1-520733792576}" name="Promedio" dataDxfId="93"/>
+    <tableColumn id="4" xr3:uid="{E2517CD1-8726-4109-92FB-1238481C74D3}" name="Peso (%)" dataDxfId="92"/>
+    <tableColumn id="5" xr3:uid="{A0A4FC88-C1B8-42FD-903E-A07CA6E46E3B}" name="Factor Decimal" dataDxfId="91"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{11AF62AA-310D-48FE-BA1B-7667C3DBDCA7}" name="Tabla84" displayName="Tabla84" ref="A1:T6" totalsRowShown="0" headerRowDxfId="63">
-  <autoFilter ref="A1:T6" xr:uid="{11AF62AA-310D-48FE-BA1B-7667C3DBDCA7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{11AF62AA-310D-48FE-BA1B-7667C3DBDCA7}" name="Tabla84" displayName="Tabla84" ref="A1:T3" totalsRowShown="0" headerRowDxfId="90">
+  <autoFilter ref="A1:T3" xr:uid="{11AF62AA-310D-48FE-BA1B-7667C3DBDCA7}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{7FA43690-F5EB-4E13-9A58-77BAB90416EE}" name="Procesos"/>
     <tableColumn id="6" xr3:uid="{3A89EFDD-17C0-4B54-957C-0FB52980B7A3}" name="Líder"/>
-    <tableColumn id="15" xr3:uid="{C0D29E03-98F1-416D-A2E5-131F3BEE4DBF}" name="¿Contenido dentro de una iniciativa?" dataDxfId="62"/>
-    <tableColumn id="19" xr3:uid="{47B3B8AD-4B8C-4C6D-BCC7-59727929E1A4}" name="Fecha Iniciativa" dataDxfId="61"/>
-    <tableColumn id="2" xr3:uid="{B2387C4F-5517-485B-95EB-0E5682BCFF4F}" name="Status del proceso" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{33557364-A07A-43F2-B9D5-50D87CC9B584}" name="Complejidad" dataDxfId="59">
+    <tableColumn id="15" xr3:uid="{C0D29E03-98F1-416D-A2E5-131F3BEE4DBF}" name="¿Contenido dentro de una iniciativa?" dataDxfId="89"/>
+    <tableColumn id="19" xr3:uid="{47B3B8AD-4B8C-4C6D-BCC7-59727929E1A4}" name="Fecha Iniciativa" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{B2387C4F-5517-485B-95EB-0E5682BCFF4F}" name="Status del proceso" dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{33557364-A07A-43F2-B9D5-50D87CC9B584}" name="Complejidad" dataDxfId="86">
       <calculatedColumnFormula>Tabla4[[#This Row],[Puntaje Final (1-10)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B515DA5E-9024-4A84-9E3E-200AE8C34D77}" name="To-be" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{69145EA3-07F3-466C-8301-64DBA9013D74}" name="As-is" dataDxfId="57"/>
-    <tableColumn id="5" xr3:uid="{15205F52-713C-4013-928A-E256171033FA}" name="Notas" dataDxfId="56"/>
-    <tableColumn id="14" xr3:uid="{FAD82E3E-F21A-49A8-828D-964A9BF62134}" name="Levantar información" dataDxfId="55"/>
-    <tableColumn id="13" xr3:uid="{F8EA1DDC-874A-4E16-8657-C5CF9979654B}" name="Armar diagrama" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{FAA1E2CD-B097-4C74-8452-0DE0D7CADB1B}" name="Validar diagrama" dataDxfId="53"/>
-    <tableColumn id="7" xr3:uid="{A2BB0178-D23F-4179-A0B4-0F8F082A21EC}" name="Mejorar proceso" dataDxfId="52"/>
-    <tableColumn id="9" xr3:uid="{EBC42DD4-CA09-42D7-875D-C7B836DAE820}" name="Validar mejora" dataDxfId="51"/>
-    <tableColumn id="12" xr3:uid="{FA384004-9376-4186-BC5E-AFD808EE03B1}" name="Implementación" dataDxfId="50"/>
-    <tableColumn id="16" xr3:uid="{D7F47828-C923-49B4-932F-3DB282948A1A}" name="% de avance" dataDxfId="49" dataCellStyle="Porcentaje">
-      <calculatedColumnFormula array="1">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{B515DA5E-9024-4A84-9E3E-200AE8C34D77}" name="To-be" dataDxfId="85"/>
+    <tableColumn id="11" xr3:uid="{69145EA3-07F3-466C-8301-64DBA9013D74}" name="As-is" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{15205F52-713C-4013-928A-E256171033FA}" name="Notas" dataDxfId="83"/>
+    <tableColumn id="14" xr3:uid="{FAD82E3E-F21A-49A8-828D-964A9BF62134}" name="Levantar información" dataDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{F8EA1DDC-874A-4E16-8657-C5CF9979654B}" name="Armar diagrama" dataDxfId="81"/>
+    <tableColumn id="8" xr3:uid="{FAA1E2CD-B097-4C74-8452-0DE0D7CADB1B}" name="Validar diagrama" dataDxfId="80"/>
+    <tableColumn id="7" xr3:uid="{A2BB0178-D23F-4179-A0B4-0F8F082A21EC}" name="Mejorar proceso" dataDxfId="79"/>
+    <tableColumn id="9" xr3:uid="{EBC42DD4-CA09-42D7-875D-C7B836DAE820}" name="Validar mejora" dataDxfId="78"/>
+    <tableColumn id="12" xr3:uid="{FA384004-9376-4186-BC5E-AFD808EE03B1}" name="Implementación" dataDxfId="77"/>
+    <tableColumn id="16" xr3:uid="{D7F47828-C923-49B4-932F-3DB282948A1A}" name="% de avance" dataDxfId="76" dataCellStyle="Porcentaje">
+      <calculatedColumnFormula array="1">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$8:$N$13))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{8DF0493C-09A5-43BB-A83A-1C98E2FF5170}" name="Fecha Inicio" dataDxfId="48" dataCellStyle="Porcentaje"/>
-    <tableColumn id="10" xr3:uid="{DD10AE7F-0B7F-4F4B-A4D5-8CFBFE66E665}" name="Tiempo bruto de levantamiento " dataDxfId="47">
+    <tableColumn id="20" xr3:uid="{8DF0493C-09A5-43BB-A83A-1C98E2FF5170}" name="Fecha Inicio" dataDxfId="75" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{DD10AE7F-0B7F-4F4B-A4D5-8CFBFE66E665}" name="Tiempo bruto de levantamiento " dataDxfId="74">
       <calculatedColumnFormula>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{BD00BC4D-A4D2-412C-B776-527EE547F3EC}" name="Tiempo especifico en semanas" dataDxfId="46">
+    <tableColumn id="17" xr3:uid="{BD00BC4D-A4D2-412C-B776-527EE547F3EC}" name="Tiempo especifico en semanas" dataDxfId="73">
       <calculatedColumnFormula>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{6DEBBB95-676A-499F-8140-11974486632D}" name="Tiempo en meses" dataDxfId="45">
+    <tableColumn id="18" xr3:uid="{6DEBBB95-676A-499F-8140-11974486632D}" name="Tiempo en meses" dataDxfId="72">
       <calculatedColumnFormula>(6.5 + (F2 - 1) * 0.9444) / 4.345</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5308,51 +5329,51 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B71FA8F6-2F96-4D6F-BEBD-C09F4167A1E7}" name="Tabla35" displayName="Tabla35" ref="J10:N17" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" headerRowBorderDxfId="41" tableBorderDxfId="42" totalsRowBorderDxfId="40">
-  <autoFilter ref="J10:N17" xr:uid="{B71FA8F6-2F96-4D6F-BEBD-C09F4167A1E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B71FA8F6-2F96-4D6F-BEBD-C09F4167A1E7}" name="Tabla35" displayName="Tabla35" ref="J7:N14" totalsRowShown="0" headerRowDxfId="71" dataDxfId="69" headerRowBorderDxfId="70" tableBorderDxfId="68" totalsRowBorderDxfId="67">
+  <autoFilter ref="J7:N14" xr:uid="{B71FA8F6-2F96-4D6F-BEBD-C09F4167A1E7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E5E47028-4EB2-47E1-A331-EF8793193E4B}" name="Columna" dataDxfId="39"/>
-    <tableColumn id="2" xr3:uid="{DC99D347-F09A-479C-B803-5B418CBC48F2}" name="Celda" dataDxfId="38"/>
-    <tableColumn id="3" xr3:uid="{66A59C75-60FC-4A2D-BA85-3D09A690AD13}" name="Promedio" dataDxfId="37"/>
-    <tableColumn id="4" xr3:uid="{0B44A7A1-1887-4359-BF73-914FF1126694}" name="Peso (%)" dataDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{E5EDC793-95B4-46D2-B220-2B6353EC5DD4}" name="Factor Decimal" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{E5E47028-4EB2-47E1-A331-EF8793193E4B}" name="Columna" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{DC99D347-F09A-479C-B803-5B418CBC48F2}" name="Celda" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{66A59C75-60FC-4A2D-BA85-3D09A690AD13}" name="Promedio" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{0B44A7A1-1887-4359-BF73-914FF1126694}" name="Peso (%)" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{E5EDC793-95B4-46D2-B220-2B6353EC5DD4}" name="Factor Decimal" dataDxfId="62"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}" name="Tabla8" displayName="Tabla8" ref="A1:T6" totalsRowShown="0" headerRowDxfId="119">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}" name="Tabla8" displayName="Tabla8" ref="A1:T6" totalsRowShown="0" headerRowDxfId="61">
   <autoFilter ref="A1:T6" xr:uid="{F462434C-157C-4CBF-96D0-05B49173FCFD}"/>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{9D6B40D3-3215-4E98-A9FC-D478FB63C1BA}" name="Procesos"/>
     <tableColumn id="6" xr3:uid="{F5B3BD05-8E49-49F1-93DE-92D27F1C49E6}" name="Líder"/>
-    <tableColumn id="15" xr3:uid="{1EA989C9-73CA-4A22-B626-AC262B041ED9}" name="¿Contenido dentro de una iniciativa?" dataDxfId="118"/>
-    <tableColumn id="19" xr3:uid="{C9D6E896-9CBC-4057-9F81-12423CB4D99E}" name="Fecha Iniciativa" dataDxfId="117"/>
-    <tableColumn id="2" xr3:uid="{EEDD7810-0171-43A9-9288-43A6DF88CC68}" name="Status del proceso" dataDxfId="116"/>
-    <tableColumn id="3" xr3:uid="{234448FA-6E6F-424A-931A-3653E7178265}" name="Complejidad" dataDxfId="115">
+    <tableColumn id="15" xr3:uid="{1EA989C9-73CA-4A22-B626-AC262B041ED9}" name="¿Contenido dentro de una iniciativa?" dataDxfId="60"/>
+    <tableColumn id="19" xr3:uid="{C9D6E896-9CBC-4057-9F81-12423CB4D99E}" name="Fecha Iniciativa" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{EEDD7810-0171-43A9-9288-43A6DF88CC68}" name="Status del proceso" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{234448FA-6E6F-424A-931A-3653E7178265}" name="Complejidad" dataDxfId="57">
       <calculatedColumnFormula>Tabla4[[#This Row],[Puntaje Final (1-10)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{5A4FFE81-7563-4F38-8BE5-EA30FC7C196D}" name="To-be" dataDxfId="114"/>
-    <tableColumn id="11" xr3:uid="{35D54FDE-D4BF-4FD2-9479-B2182C98B6D5}" name="As-is" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{E6EB2333-E84F-41CE-8EAC-52D77BF66F44}" name="Notas" dataDxfId="112"/>
-    <tableColumn id="14" xr3:uid="{8112EDF6-BC89-4919-A355-D2D3D1BF34BA}" name="Levantar información" dataDxfId="111"/>
-    <tableColumn id="13" xr3:uid="{2EA9FA24-C3F1-4C14-A867-A6FAC65E747C}" name="Armar diagrama" dataDxfId="110"/>
-    <tableColumn id="8" xr3:uid="{CD6D287B-BCEC-45D9-8EB8-A0F76A9F8CAF}" name="Validar diagrama" dataDxfId="109"/>
-    <tableColumn id="7" xr3:uid="{F4FF766B-5291-4082-A0FF-A66586E7C142}" name="Mejorar proceso" dataDxfId="108"/>
-    <tableColumn id="9" xr3:uid="{0C5A0591-A510-455E-AD87-7F86245A682D}" name="Validar mejora" dataDxfId="107"/>
-    <tableColumn id="12" xr3:uid="{C63E8C68-557E-49A9-8D27-236FDCB340BC}" name="Implementación" dataDxfId="106"/>
-    <tableColumn id="16" xr3:uid="{8B4C9571-AFDF-4088-806A-0420B7E2442E}" name="% de avance" dataDxfId="105" dataCellStyle="Porcentaje">
+    <tableColumn id="4" xr3:uid="{5A4FFE81-7563-4F38-8BE5-EA30FC7C196D}" name="To-be" dataDxfId="56"/>
+    <tableColumn id="11" xr3:uid="{35D54FDE-D4BF-4FD2-9479-B2182C98B6D5}" name="As-is" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{E6EB2333-E84F-41CE-8EAC-52D77BF66F44}" name="Notas" dataDxfId="54"/>
+    <tableColumn id="14" xr3:uid="{8112EDF6-BC89-4919-A355-D2D3D1BF34BA}" name="Levantar información" dataDxfId="53"/>
+    <tableColumn id="13" xr3:uid="{2EA9FA24-C3F1-4C14-A867-A6FAC65E747C}" name="Armar diagrama" dataDxfId="52"/>
+    <tableColumn id="8" xr3:uid="{CD6D287B-BCEC-45D9-8EB8-A0F76A9F8CAF}" name="Validar diagrama" dataDxfId="51"/>
+    <tableColumn id="7" xr3:uid="{F4FF766B-5291-4082-A0FF-A66586E7C142}" name="Mejorar proceso" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{0C5A0591-A510-455E-AD87-7F86245A682D}" name="Validar mejora" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{C63E8C68-557E-49A9-8D27-236FDCB340BC}" name="Implementación" dataDxfId="48"/>
+    <tableColumn id="16" xr3:uid="{8B4C9571-AFDF-4088-806A-0420B7E2442E}" name="% de avance" dataDxfId="47" dataCellStyle="Porcentaje">
       <calculatedColumnFormula array="1">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{7CE675F8-BCC9-4D91-AE6F-A7A6A1C260DD}" name="Fecha Inicio" dataDxfId="104" dataCellStyle="Porcentaje"/>
-    <tableColumn id="10" xr3:uid="{B6DD48A4-1AB9-4C6E-A7E2-D52D8502F05C}" name="Tiempo bruto de levantamiento " dataDxfId="103">
+    <tableColumn id="20" xr3:uid="{7CE675F8-BCC9-4D91-AE6F-A7A6A1C260DD}" name="Fecha Inicio" dataDxfId="46" dataCellStyle="Porcentaje"/>
+    <tableColumn id="10" xr3:uid="{B6DD48A4-1AB9-4C6E-A7E2-D52D8502F05C}" name="Tiempo bruto de levantamiento " dataDxfId="45">
       <calculatedColumnFormula>IF(F2&lt;=3, 6.5, IF(F2&lt;=7, 10.5, 15))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{97833884-FD4C-49EA-8567-FE1DD15B1ED4}" name="Tiempo especifico en semanas" dataDxfId="102">
+    <tableColumn id="17" xr3:uid="{97833884-FD4C-49EA-8567-FE1DD15B1ED4}" name="Tiempo especifico en semanas" dataDxfId="44">
       <calculatedColumnFormula>6.5 + (F2 - 1) * ((15 - 6.5) / (10 - 1))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{79F26D04-CE30-49F5-B63D-964F30F64CC4}" name="Tiempo en meses" dataDxfId="101">
+    <tableColumn id="18" xr3:uid="{79F26D04-CE30-49F5-B63D-964F30F64CC4}" name="Tiempo en meses" dataDxfId="43">
       <calculatedColumnFormula>(6.5 + (F2 - 1) * 0.9444) / 4.345</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5361,33 +5382,33 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}" name="Tabla3" displayName="Tabla3" ref="J10:N17" totalsRowShown="0" headerRowDxfId="100" dataDxfId="98" headerRowBorderDxfId="99" tableBorderDxfId="97" totalsRowBorderDxfId="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}" name="Tabla3" displayName="Tabla3" ref="J10:N17" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
   <autoFilter ref="J10:N17" xr:uid="{1F61AF38-83D6-494E-8F97-F9D6A5B867B2}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{22A678DC-4FD4-457E-BF2F-A5B26AF5A9EF}" name="Columna" dataDxfId="95"/>
-    <tableColumn id="2" xr3:uid="{20414C72-C442-4898-9B74-EA7858B03946}" name="Celda" dataDxfId="94"/>
-    <tableColumn id="3" xr3:uid="{BA1EDFE7-FD4C-4A18-B24F-51500610B0F3}" name="Promedio" dataDxfId="93"/>
-    <tableColumn id="4" xr3:uid="{18E92589-EFEA-448D-8CFF-7A861810DB8E}" name="Peso (%)" dataDxfId="92"/>
-    <tableColumn id="5" xr3:uid="{D9FEA8B4-A59E-4AC5-9FA6-A99F7AA97E09}" name="Factor Decimal" dataDxfId="91"/>
+    <tableColumn id="1" xr3:uid="{22A678DC-4FD4-457E-BF2F-A5B26AF5A9EF}" name="Columna" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{20414C72-C442-4898-9B74-EA7858B03946}" name="Celda" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{BA1EDFE7-FD4C-4A18-B24F-51500610B0F3}" name="Promedio" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{18E92589-EFEA-448D-8CFF-7A861810DB8E}" name="Peso (%)" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{D9FEA8B4-A59E-4AC5-9FA6-A99F7AA97E09}" name="Factor Decimal" dataDxfId="33"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4FD466F-89DF-47BA-AC9E-559F47CB9595}" name="Tabla4" displayName="Tabla4" ref="A1:H6" totalsRowShown="0" headerRowDxfId="90">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A4FD466F-89DF-47BA-AC9E-559F47CB9595}" name="Tabla4" displayName="Tabla4" ref="A1:H6" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="A1:H6" xr:uid="{A4FD466F-89DF-47BA-AC9E-559F47CB9595}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{209BC8CE-A4E5-4EAD-9176-25919D421EE7}" name="Proceso" dataDxfId="89"/>
-    <tableColumn id="2" xr3:uid="{AD141033-AAC8-430E-AED3-EE13742AEDEF}" name="Áreas Involucradas (25%)" dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{81BAF825-E86C-4EAB-83B0-4BEF6E690DAF}" name="Contenido dentro de una iniciativa (20%)" dataDxfId="87"/>
-    <tableColumn id="5" xr3:uid="{BD9A8428-D2BF-47C3-8A4D-000DDA7085B1}" name="¿Requiere desarrollo tecnologico? (20%)" dataDxfId="86"/>
-    <tableColumn id="6" xr3:uid="{CC386173-731D-4092-A2CC-5DFC807607AC}" name="¿Es un levantamiento nuevo? (15%)" dataDxfId="85"/>
-    <tableColumn id="7" xr3:uid="{44DB2B51-5EBC-435E-B533-35DBC727260D}" name="¿Toca un proceso clave? (20%)" dataDxfId="84"/>
-    <tableColumn id="8" xr3:uid="{91CAEE15-D755-4AEE-BD7E-76CF718F3FEF}" name="Puntaje Final (1-10)" dataDxfId="83">
+    <tableColumn id="1" xr3:uid="{209BC8CE-A4E5-4EAD-9176-25919D421EE7}" name="Proceso" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{AD141033-AAC8-430E-AED3-EE13742AEDEF}" name="Áreas Involucradas (25%)" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{81BAF825-E86C-4EAB-83B0-4BEF6E690DAF}" name="Contenido dentro de una iniciativa (20%)" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{BD9A8428-D2BF-47C3-8A4D-000DDA7085B1}" name="¿Requiere desarrollo tecnologico? (20%)" dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{CC386173-731D-4092-A2CC-5DFC807607AC}" name="¿Es un levantamiento nuevo? (15%)" dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{44DB2B51-5EBC-435E-B533-35DBC727260D}" name="¿Toca un proceso clave? (20%)" dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{91CAEE15-D755-4AEE-BD7E-76CF718F3FEF}" name="Puntaje Final (1-10)" dataDxfId="25">
       <calculatedColumnFormula>IF(B2="", "", 10 * ( (MATCH(B2, {"1-2";"3-4";"4+"}, 0)/3)*0.25 + N(C2)*0.2 + N(D2)*0.2 + N(E2)*0.15 + N(F2)*0.2 ))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{83E13230-22E5-49E0-9B92-C34352FB3731}" name="Complejidad" dataDxfId="82">
+    <tableColumn id="4" xr3:uid="{83E13230-22E5-49E0-9B92-C34352FB3731}" name="Complejidad" dataDxfId="24">
       <calculatedColumnFormula>+IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&lt;=4,"Baja",IF(Tabla4[[#This Row],[Puntaje Final (1-10)]]&gt;7,"Alta","Media"))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5747,7 +5768,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C2" s="19" t="b">
         <v>0</v>
@@ -5807,7 +5828,7 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="C3" s="19" t="b">
         <v>0</v>
@@ -5867,7 +5888,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="23" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="C4" s="19" t="b">
         <v>0</v>
@@ -5927,7 +5948,7 @@
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C5" s="19" t="b">
         <v>0</v>
@@ -5987,7 +6008,7 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="B6" s="33"/>
       <c r="C6" s="19" t="b">
@@ -6394,24 +6415,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:D6">
-    <cfRule type="expression" dxfId="34" priority="6">
+    <cfRule type="expression" dxfId="23" priority="6">
       <formula>$H2=TRUE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="7">
+    <cfRule type="expression" dxfId="22" priority="7">
       <formula>$G2=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="8">
+    <cfRule type="expression" dxfId="21" priority="8">
       <formula>$G2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E6 E13:E41">
-    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
       <formula>"Listo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
       <formula>"No iniciado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="5" operator="equal">
       <formula>"En curso"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6523,7 +6544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05CDFC9F-E2B1-4FD0-B740-E450CA39F138}">
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:T38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:20" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6590,7 +6611,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="C2" s="19" t="b">
         <v>0</v>
@@ -6629,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="25" cm="1">
-        <f t="array" ref="P2">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$11:$N$16))</f>
+        <f t="array" ref="P2">+SUMPRODUCT(--(J2:O2),TRANSPOSE($N$8:$N$13))</f>
         <v>0.76560000000000006</v>
       </c>
       <c r="Q2" s="41">
@@ -6650,7 +6671,7 @@
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C3" s="19" t="b">
         <v>0</v>
@@ -6689,7 +6710,7 @@
         <v>0</v>
       </c>
       <c r="P3" s="25" cm="1">
-        <f t="array" ref="P3">+SUMPRODUCT(--(J3:O3),TRANSPOSE($N$11:$N$16))</f>
+        <f t="array" ref="P3">+SUMPRODUCT(--(J3:O3),TRANSPOSE($N$8:$N$13))</f>
         <v>0.3906</v>
       </c>
       <c r="Q3" s="41">
@@ -6709,492 +6730,324 @@
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A4" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" s="38"/>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="16">
-        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
-        <v>6.0000000000000009</v>
-      </c>
-      <c r="G4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P4" s="25" cm="1">
-        <f t="array" ref="P4">+SUMPRODUCT(--(J4:O4),TRANSPOSE($N$11:$N$16))</f>
-        <v>0.3906</v>
-      </c>
-      <c r="Q4" s="41">
-        <v>46006</v>
-      </c>
-      <c r="R4" s="3">
-        <f>IF(F4&lt;=3, 6.5, IF(F4&lt;=7, 10.5, 15))</f>
-        <v>10.5</v>
-      </c>
-      <c r="S4" s="6">
-        <f>6.5 + (F4 - 1) * ((15 - 6.5) / (10 - 1))</f>
-        <v>11.222222222222223</v>
-      </c>
-      <c r="T4" s="6">
-        <f>(6.5 + (F4 - 1) * 0.9444) / 4.345</f>
-        <v>2.5827387802071349</v>
-      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="Q4" s="40"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D5" s="38"/>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="16">
-        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
-        <v>2.5</v>
-      </c>
-      <c r="G5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5" s="25" cm="1">
-        <f t="array" ref="P5">+SUMPRODUCT(--(J5:O5),TRANSPOSE($N$11:$N$16))</f>
-        <v>0.53120000000000001</v>
-      </c>
-      <c r="Q5" s="41">
-        <v>46027</v>
-      </c>
-      <c r="R5" s="3">
-        <f>IF(F5&lt;=3, 6.5, IF(F5&lt;=7, 10.5, 15))</f>
-        <v>6.5</v>
-      </c>
-      <c r="S5" s="6">
-        <f>6.5 + (F5 - 1) * ((15 - 6.5) / (10 - 1))</f>
-        <v>7.9166666666666661</v>
-      </c>
-      <c r="T5" s="6">
-        <f>(6.5 + (F5 - 1) * 0.9444) / 4.345</f>
-        <v>1.8220023014959725</v>
-      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="Q5" s="40"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D6" s="38"/>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="16">
-        <f>Tabla4[[#This Row],[Puntaje Final (1-10)]]</f>
-        <v>4.5</v>
-      </c>
-      <c r="G6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3"/>
-      <c r="J6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P6" s="25" cm="1">
-        <f t="array" ref="P6">+SUMPRODUCT(--(J6:O6),TRANSPOSE($N$11:$N$16))</f>
-        <v>0.1875</v>
-      </c>
-      <c r="Q6" s="41">
-        <v>46048</v>
-      </c>
-      <c r="R6" s="3">
-        <f>IF(F6&lt;=3, 6.5, IF(F6&lt;=7, 10.5, 15))</f>
-        <v>10.5</v>
-      </c>
-      <c r="S6" s="6">
-        <f>6.5 + (F6 - 1) * ((15 - 6.5) / (10 - 1))</f>
-        <v>9.8055555555555554</v>
-      </c>
-      <c r="T6" s="6">
-        <f>(6.5 + (F6 - 1) * 0.9444) / 4.345</f>
-        <v>2.2567088607594941</v>
-      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="Q6" s="40"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C7" s="13"/>
       <c r="D7" s="39"/>
-      <c r="E7" s="13"/>
+      <c r="E7" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>30</v>
+      </c>
       <c r="Q7" s="40"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C8" s="13"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="Q8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="29">
+        <v>2</v>
+      </c>
+      <c r="M8" s="30">
+        <v>0.1875</v>
+      </c>
+      <c r="N8" s="11">
+        <v>0.1875</v>
+      </c>
+      <c r="P8" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q8" s="44">
+        <v>0.1875</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C9" s="13"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="Q9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="29">
+        <v>0.67</v>
+      </c>
+      <c r="M9" s="30">
+        <v>6.25E-2</v>
+      </c>
+      <c r="N9" s="11">
+        <v>6.25E-2</v>
+      </c>
+      <c r="P9" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q9" s="45">
+        <v>6.25E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C10" s="13"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="M10" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="N10" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q10" s="40"/>
+      <c r="B10" s="4"/>
+      <c r="D10" s="40"/>
+      <c r="F10" s="34"/>
+      <c r="J10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="M10" s="30">
+        <v>0.1406</v>
+      </c>
+      <c r="N10" s="11">
+        <v>0.1406</v>
+      </c>
+      <c r="P10" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q10" s="44">
+        <v>0.1406</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B11" s="4"/>
       <c r="D11" s="40"/>
-      <c r="E11" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="13"/>
+      <c r="F11" s="33"/>
       <c r="J11" s="12" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="K11" s="8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L11" s="29">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M11" s="30">
-        <v>0.1875</v>
+        <v>0.375</v>
       </c>
       <c r="N11" s="11">
-        <v>0.1875</v>
-      </c>
-      <c r="P11" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q11" s="44">
-        <v>0.1875</v>
+        <v>0.375</v>
+      </c>
+      <c r="P11" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="45">
+        <v>0.375</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B12" s="4"/>
       <c r="D12" s="40"/>
-      <c r="E12" s="18" t="s">
-        <v>34</v>
-      </c>
+      <c r="G12" s="33"/>
       <c r="J12" s="12" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="L12" s="29">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="M12" s="30">
-        <v>6.25E-2</v>
+        <v>0.1406</v>
       </c>
       <c r="N12" s="11">
-        <v>6.25E-2</v>
-      </c>
-      <c r="P12" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q12" s="45">
-        <v>6.25E-2</v>
+        <v>0.1406</v>
+      </c>
+      <c r="P12" s="42" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q12" s="44">
+        <v>0.1406</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B13" s="4"/>
       <c r="D13" s="40"/>
-      <c r="F13" s="34"/>
       <c r="J13" s="12" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L13" s="29">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M13" s="30">
-        <v>0.1406</v>
+        <v>9.3799999999999994E-2</v>
       </c>
       <c r="N13" s="11">
-        <v>0.1406</v>
-      </c>
-      <c r="P13" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q13" s="44">
-        <v>0.1406</v>
+        <v>9.3799999999999994E-2</v>
+      </c>
+      <c r="P13" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q13" s="45">
+        <v>9.3799999999999994E-2</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B14" s="4"/>
       <c r="D14" s="40"/>
-      <c r="F14" s="33"/>
-      <c r="J14" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="L14" s="29">
-        <v>4</v>
-      </c>
-      <c r="M14" s="30">
-        <v>0.375</v>
+      <c r="J14" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="K14" s="32"/>
+      <c r="L14" s="9">
+        <v>10.67</v>
+      </c>
+      <c r="M14" s="10">
+        <v>1</v>
       </c>
       <c r="N14" s="11">
-        <v>0.375</v>
-      </c>
-      <c r="P14" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q14" s="45">
-        <v>0.375</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q14" s="40"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B15" s="4"/>
       <c r="D15" s="40"/>
-      <c r="J15" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="L15" s="29">
-        <v>1.5</v>
-      </c>
-      <c r="M15" s="30">
-        <v>0.1406</v>
-      </c>
-      <c r="N15" s="11">
-        <v>0.1406</v>
-      </c>
-      <c r="P15" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q15" s="44">
-        <v>0.1406</v>
-      </c>
+      <c r="Q15" s="40"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B16" s="4"/>
       <c r="D16" s="40"/>
-      <c r="J16" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L16" s="29">
-        <v>1</v>
-      </c>
-      <c r="M16" s="30">
-        <v>9.3799999999999994E-2</v>
-      </c>
-      <c r="N16" s="11">
-        <v>9.3799999999999994E-2</v>
-      </c>
-      <c r="P16" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q16" s="45">
-        <v>9.3799999999999994E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.35">
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="40"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17" s="4"/>
       <c r="D17" s="40"/>
-      <c r="J17" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="K17" s="32"/>
-      <c r="L17" s="9">
-        <v>10.67</v>
-      </c>
-      <c r="M17" s="10">
-        <v>1</v>
-      </c>
-      <c r="N17" s="11">
-        <v>1</v>
-      </c>
+      <c r="N17" s="24"/>
       <c r="Q17" s="40"/>
     </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18" s="4"/>
       <c r="D18" s="40"/>
+      <c r="N18" s="24"/>
       <c r="Q18" s="40"/>
     </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" s="4"/>
       <c r="D19" s="40"/>
       <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
       <c r="Q19" s="40"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" s="4"/>
       <c r="D20" s="40"/>
       <c r="N20" s="24"/>
       <c r="Q20" s="40"/>
     </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B21" s="4"/>
       <c r="D21" s="40"/>
       <c r="N21" s="24"/>
       <c r="Q21" s="40"/>
     </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B22" s="4"/>
       <c r="D22" s="40"/>
       <c r="N22" s="24"/>
       <c r="Q22" s="40"/>
     </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B23" s="4"/>
       <c r="D23" s="40"/>
-      <c r="N23" s="24"/>
       <c r="Q23" s="40"/>
     </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B24" s="4"/>
       <c r="D24" s="40"/>
-      <c r="N24" s="24"/>
       <c r="Q24" s="40"/>
     </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B25" s="4"/>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D25" s="40"/>
-      <c r="N25" s="24"/>
       <c r="Q25" s="40"/>
     </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B26" s="4"/>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D26" s="40"/>
       <c r="Q26" s="40"/>
     </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.35">
-      <c r="B27" s="4"/>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D27" s="40"/>
       <c r="Q27" s="40"/>
     </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D28" s="40"/>
       <c r="Q28" s="40"/>
     </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D29" s="40"/>
       <c r="Q29" s="40"/>
     </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D30" s="40"/>
       <c r="Q30" s="40"/>
     </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D31" s="40"/>
       <c r="Q31" s="40"/>
     </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
       <c r="D32" s="40"/>
       <c r="Q32" s="40"/>
     </row>
@@ -7222,43 +7075,31 @@
       <c r="D38" s="40"/>
       <c r="Q38" s="40"/>
     </row>
-    <row r="39" spans="4:17" x14ac:dyDescent="0.35">
-      <c r="D39" s="40"/>
-      <c r="Q39" s="40"/>
-    </row>
-    <row r="40" spans="4:17" x14ac:dyDescent="0.35">
-      <c r="D40" s="40"/>
-      <c r="Q40" s="40"/>
-    </row>
-    <row r="41" spans="4:17" x14ac:dyDescent="0.35">
-      <c r="D41" s="40"/>
-      <c r="Q41" s="40"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:D6">
-    <cfRule type="expression" dxfId="69" priority="6">
+  <conditionalFormatting sqref="A2:D3">
+    <cfRule type="expression" dxfId="17" priority="6">
       <formula>$H2=TRUE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="7">
+    <cfRule type="expression" dxfId="16" priority="7">
       <formula>$G2=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="8">
+    <cfRule type="expression" dxfId="15" priority="8">
       <formula>$G2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:E6 E13:E41">
-    <cfRule type="cellIs" dxfId="66" priority="3" operator="equal">
+  <conditionalFormatting sqref="E1:E3 E10:E38">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>"Listo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"No iniciado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
       <formula>"En curso"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="F2:F3">
+    <cfRule type="colorScale" priority="101">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7269,8 +7110,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R6">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="R2:R3">
+    <cfRule type="colorScale" priority="102">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7281,8 +7122,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:S6">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="R2:S3">
+    <cfRule type="colorScale" priority="103">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7293,8 +7134,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S6">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="S2:S3">
+    <cfRule type="colorScale" priority="104">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7305,8 +7146,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T6 R2:R6">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="T2:T3 R2:R3">
+    <cfRule type="colorScale" priority="105">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7317,8 +7158,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T6">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="T2:T3">
+    <cfRule type="colorScale" priority="107">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7328,7 +7169,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="108">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7338,7 +7179,7 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="109">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7350,7 +7191,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E6" xr:uid="{BF64BDE7-CBAB-4F78-81B2-E23F87FF287C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E3" xr:uid="{BF64BDE7-CBAB-4F78-81B2-E23F87FF287C}">
       <formula1>"No iniciado,En curso,Listo"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8000,24 +7841,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:D6">
-    <cfRule type="expression" dxfId="81" priority="23">
+    <cfRule type="expression" dxfId="11" priority="23">
       <formula>$H2=TRUE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="24">
+    <cfRule type="expression" dxfId="10" priority="24">
       <formula>$G2=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="25">
+    <cfRule type="expression" dxfId="9" priority="25">
       <formula>$G2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E6 E13:E1048576">
-    <cfRule type="cellIs" dxfId="78" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"Listo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="77" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"No iniciado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>"En curso"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8336,24 +8177,24 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A6">
-    <cfRule type="expression" dxfId="75" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
       <formula>$H2=TRUE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$G2=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="3">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>$G2=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D4">
-    <cfRule type="cellIs" dxfId="72" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"Listo"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="71" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="8" operator="equal">
       <formula>"No iniciado"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
       <formula>"En curso"</formula>
     </cfRule>
   </conditionalFormatting>
